--- a/data/processed/상상대로_신규수집_출산양육후보_검증용_ver2.xlsx
+++ b/data/processed/상상대로_신규수집_출산양육후보_검증용_ver2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R138"/>
+  <dimension ref="A1:T138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,16 @@
           <t>제외사유</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>웹크롤링_상세본문</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>크롤링상태</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -541,10 +551,8 @@
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="E2" t="n">
+        <v>2026</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -603,6 +611,23 @@
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>제안 배경:
+관내 실내 빙상장 부족으로 인한 동호인 및 청소년 체육 환경 열악.
+도심 기피 시설인 유수지 공간을 복개하여 주민 친화적 생활 SOC로 전환 필요.
+기대 효과 (차별성):
+부지 비용 '0원':
+신규 토지 매입 없이 기존 시유지/구유지(유수지)를 활용해 수백억 원의 예산 절감.
+친환경 에너지 모델:
+빗물 정화수를 활용한 고품질 빙질 유지 및 하수/유수 수열 에너지를 이용한 냉동기 가동 (탄소중립 실현 및 운영비 혁신적 감축).</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -625,10 +650,8 @@
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="E3" t="n">
+        <v>2026</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -687,6 +710,34 @@
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>“
+유아숲체험원 운영 용역사업의 제안 평가는
+영유아를 대상으로 하는
+“
+특정 대상
+”
+인 것 만큼
+,
+‘
+잘 만든 제안서
+’
+가 아니라
+,
+영유아의 발달 특성과 안전을 실제 구현할 수 있는
+열심하는 유아숲지도사의 숲 현장 노력과
+전문성 중심
+으로
+재편되어야 합니다
+.”</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -709,10 +760,8 @@
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="E4" t="n">
+        <v>2026</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -771,6 +820,127 @@
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>서울시장 당선인님께
+안녕하십니까
+.
+BTF
+푸른나무재단입니다
+.
+먼저 제
+9
+회 전국동시지방선거 지방자치단체장 당선을 진심으로 축하드립니다
+.
+BTF
+푸른나무재단은
+1995
+년 학교폭력 피해로 아들을 잃은 아버지의 간절한 염원에서 시작되어
+,
+지난
+30
+년간 학교폭력 예방과 피해학생 치유
+,
+정책 제안과 사회변화 활동을 이어온 비영리공익법인입니다
+.
+지금 학교폭력은 다시 중요한 전환점에 놓여 있습니다
+.
+학교폭력의 저연령화
+,
+반복 피해
+·
+가해 증가
+,
+도움요청 감소
+,
+침묵과 방관의 확대는 학교가 아이들에게 충분히 안전한 공간인지 다시 묻게 하고 있습니다
+.
+학교폭력 대응은 더 이상 사건 발생 이후의 처리에만 머물 수 없습니다
+.
+예방
+,
+조기 발견
+,
+피해학생 보호와 회복
+,
+가해학생의 책임 있는 변화
+,
+학교와 지역사회의 연계가 함께 작동해야 합니다
+.
+이에
+BTF
+푸른나무재단은 당선인님의 취임 이후
+지역사회에서
+학교폭력 예방 및 대응 과제가 주요하게 반영될 수 있도록
+「
+제
+9
+회 지방선거 지방자치단체장 당선인에게 전하는 학교폭력 예방 및 대응 정책 제안서
+」
+를 전달드립니다
+.
+이번 제안서에는 다음의
+3
+대 정책 방향을 담았습니다
+.
+&lt;
+지방자치단체장 후보자께 제안드리는
+3
+대 공약
+&gt;
+1.
+학교폭력 대응이 작동하는 지역 책임체계를 마련해야 합니다
+.
+2.
+아동
+·
+청소년의 마음건강을 위한 지역 인프라를 확충해야 합니다
+.
+3.
+학교폭력이 지역사회 갈등의 씨앗이 되지 않도록 예방해야 합니다
+.
+아이들이 안심하고 배우며 성장할 수 있는 학교를 만드는 일은 더 이상 미룰 수 없는 과제입니다
+.
+당선인님께서 속한
+지역사회 내에서 학교폭력 예방
+·
+대응 체계가 보다 구체적이고 지속 가능한 정책으로 이어질 수 있도록 깊은 관심과 검토를 부탁드립니다
+.
+첨부드리는 정책 제안서를 확인해 주시고 적극적 검토를 부탁드립니다
+.
+감사합니다
+.
+BTF
+푸른나무재단 드림
+붙임
+. [BTF
+푸른나무재단
+]
+제
+9
+회 전국동시지방선거 지방자치단체장 당선인에게 전하는 학교폭력 예방 및 대응 정책 제안서
+1
+부
+.
+끝
+.
+BTF
+푸른나무재단 홈페이지
+: https://btf.or.kr/
+BTF
+푸른나무재단 설립 스토리
+: https://youtu.be/hdrJ5OaeUFY?si=vT_-efrAbET6hhnH
+☎
+BTF
+푸른나무재단 학교폭력문제연구소
+) 02-598-1640</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -793,10 +963,8 @@
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="E5" t="n">
+        <v>2026</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -855,6 +1023,21 @@
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>안녕하세요.방과후교실에서 2026년 3월에 지역아동센터로 전환된 영성지역 아동센터 입니다.
+도로가 급경사를 이룬곳도 많으며 이동 차량도 많습니다.
+또한 우리센터 기준으로 100m 아래로 어린이집, 100m위쪽으로 청운복지관 노인시설,아동시설이 위치해 있습니다.
+현재 도로에는 30km과 방지턱이 있으나 운전자들이 인지하기엔 다소 미흡니다.
+그리고 주택가 인근이라서 주차된 차량으로 많이 표지판등이 가리워 졌습니다.그래서 6월초경 저희 센터 앞쪽에서 아동이
+반대편쪽 엄마를 보고 톡 튀어 나가 사고가 났다는 소식을 들어, 우리에게도 일어날수 있다는 생각이 들어 아이들의 안전를 위해 서울시에서 도로에어린이 안전구역임을 표지해 주시기를 간절히 요청 합니다.꼭 부탁드립니다.</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -877,10 +1060,8 @@
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="E6" t="n">
+        <v>2026</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -939,6 +1120,22 @@
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>현황 및 문제점
+어린이 보호구역내 인도의 각종 표지판 하단은 스덴으로 기둥이 되어 있어, 어린이 및 주민 식별 저하
+* 특히 최근 어린이들 도보시 스마트폰을 보면서 이동하여 표지판에 사고를 당할수 있음.
+개선방안
+어린이 보호구역 인도내 표지판의 하단에 밝은 노랑 스티커 부착으로 보행자분들께서 야간에도 식별 가능하고, 주간에도 식별이 가능하도록 개선
+기대효과
+밝은 스티커 부착으로 운전자의 시야 확보, 어린이 보호구역내 사고위험 저하, 주민들의 인도 통행시 사물 확인 용이</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -961,10 +1158,8 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="E7" t="n">
+        <v>2026</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1023,6 +1218,22 @@
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>서울시에서 운영하는 다양한 시민 참여 정책에 감사드립니다.
+저는 현재 강남구보건소에서 운영 중인 예방접종 관리 프로그램이 시민들에게 매우 유용한 서비스라고 생각합니다.  접종 안전성 측면에서 많은 도움이 되고 있어, 이러한 시스템이 다른구 보건소에도  확대되면 좋겠다는 생각이 들어 제안을 드립니다.
+저는 오접종 경헙이 있었던 사람으로서. 강남구보건소에서 시행 중인 접종전에 확실하게 사고를 방지 할수 있고 체계적으로 관리할 수 있는 시스템이 서울 전역으로 확대된다면, 접종 오류를 줄이고 시민들의 신뢰를 높이는 데 큰 도움이 될 것으로 기대됩니다.
+자치구별로 시민에서 제공하는 서비스가 틀리다는 부분이 좀 이해가 안가는 부분도 있습니다만
+타 자치구에서도 충분히 도입 가능하다고 생각하며, 서울시 차원에서 검토해 주시기를 요청드립니다.
+시민의 건강과 안전을 위한 정책에 항상 힘써주셔서 감사드리며, 본 제안이 긍정적으로 검토되기를 바랍니다.
+감사합니다.</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1045,10 +1256,8 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="E8" t="n">
+        <v>2026</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1107,6 +1316,26 @@
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>현황 및 문제점
+현재 전국의 어린이 보호구역과 이면도로에 설치된 아스팔트 과속방지턱은 안전을 명분으로 설치되었으나, 실제로는 보행자(어린이·노인)의 낙상 사고, 차량 파손, 비산먼지 발생 등 수많은 부작용을 낳고 있습니다.
+개선방안
+턱 없는(Zero-Bump) 스마트 안전 구역
+물리적으로 차를 멈추게 하는 시대는 지났습니다. 이제는 포장재의 혁신으로 스스로 서행하게 해야 합니다.
+기술적 해결 (1등급 투수블록 활용): 특정 안전 구간 전체를 시인성이 높은 색상의 고성능 투수블록으로 포장합니다. 운전자는 시각적으로 "특별 관리 구역"임을 즉각 인지하고 심리적으로 자연스러운 감속을 실천하게 됩니다.
+감성적 서행 유도: 블록 포장 고유의 노면 질감을 활용하여 운전자에게 직관적인 주의를 환기시키며, 기존 과속방지턱의 고질적 문제였던, 차량 하부 간섭 및 긁힘과 파손을 근본적으로 제거하여 주행 안전성을 보장합니다. '턱' 없이도 속도를 줄이는 과학적이고 품격있는 방법입니다.
+기후 위기 대응: 빗물을 100% 흡수하는 1등급 투수 기술은 도시 침수를 막고 열섬 현상을 해결합니다.
+기대효과
+국민 안전: 어린이·노인 낙상 사고 Zero화 및 차량 파손 민원 종결.
+탄소 중립: 아스팔트 대비 탄소 배출 저감 및 도시 물순환 회복.</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1129,10 +1358,8 @@
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="E9" t="n">
+        <v>2026</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -1191,6 +1418,32 @@
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>안녕하세요,
+도봉구 방학동에 위치한 창도초등학교 정문과 대상 아파트 사이의 횡단보도로 많은 초등학
+？
+생들이
+등하교를 하고 있습니다.
+등하교길에 이 횡단보도에 많은 차량들이 꼬리물기 신호위반 / 불법정차 등을 너무 빈번하게 하고 있어
+소중한 아이들의 안전이 매우 위태로운 상태 입니다.
+특히 행단보도 위에 꼬리물기 하고 있는 차량을 피해 좁은 차사이로 조그만 아이들이 이리저리 피해가는
+것을보면 아찔합니다.
+몇년전부터 학교 ,구청, 경찰서에 상태의 심각성을 전달 하였지만 나아 지는것이 없습니다.
+만일 심각한 사고라도 나면 누가 책임질 것이고 그때서야 조치를 취할것입니까?
+경찰이나 학교 관계자들이 계도를 해봤자 통하질 않습니다.
+위반 차량에 대해서는 무관용의 단속으로 과태료를 부과하여야 질서가 잡힐것입니다,
+또한 지속적인 단속을 위해서 횡단보도 앞에 CCTV를 설치하여 불법주정차등 법규위반 차량을 감시하여
+아이들의 안전을 지켜주십시오.
+특히 새학기에는 더욱 철저하게 단속하여야 할 것입니다.
+신속한 처리 부탁드립니다.</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1213,10 +1466,8 @@
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="E10" t="n">
+        <v>2026</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -1275,6 +1526,28 @@
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>여자화장실에는 접이식 기저귀 갈이대가 있습니다.
+남자화장실에는 기저귀 갈이대가 없습니다.
+현시대에는 엄마, 아빠 함께 육아를 하기 때문에
+우유를 먹이거나 기저귀 가는 일에 아빠도 함께합니다.
+그런데 현재 남자화장실에는 기저귀 갈이대가 없습니다.
+아빠 혼자 육아를 하는 경우가 많아졌습니다.
+남자화장실에도 기저귀갈이대가 설치되길 바랍니다.
+여아를 남자화장실에서 기저귀 갈아주기는 조금 불편하므로 유아와 아빠와 함께 사용하는
+화장실을 만들고
+그 안에 접이식 기저귀 갈이대를
+설치되길 바랍니다.
+화장실 중에는 부모와 유아가 함께 사용하는 조금 큰 화장실이 있습니다.
+아래 시군구 선택을 전체도 만들어주세요.</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1297,10 +1570,8 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="E11" t="n">
+        <v>2026</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -1359,6 +1630,16 @@
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>서울형키즈카페 형제자매 동시들어걀수있게 부탁드립니다.예를들어사당2동 서울형키즈카페의경우  21년생 들어가면 19년생도 동시 입장할수있게 부탁드립니다.</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1381,10 +1662,8 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="E12" t="n">
+        <v>2026</v>
       </c>
       <c r="F12" t="n">
         <v>2</v>
@@ -1443,6 +1722,25 @@
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1. 문제
+- 긴급 상황인데도
+사전회원 등록·서류 제출
+을 먼저 요구
+- 갑작스런 야근·질병·경조사 시 이용 어려움
+2. 개선 제안
+- 긴급일시돌봄은
+사후 서류 제출 허용
+- 보호자 신분 확인 후 즉시 이용 가능하도록 절차 단순화
+- 서울시 통합 인증(서울시민 인증)으로 자동 연계</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1465,10 +1763,8 @@
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="E13" t="n">
+        <v>2026</v>
       </c>
       <c r="F13" t="n">
         <v>4</v>
@@ -1527,6 +1823,30 @@
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>본 제안은
+어린이 보호구역(스쿨존) 인근 보도 및 이면도로에 배달 오토바이와 자전거 등 이륜차가 무분별하게 주차되어 있어 아동의 보행 안전이 심각하게 위협받고 있는 문제를 개선하고자 함
+. 실제로 성동구 경동초등학교 앞과 강동구 유정유치원 앞 어린이 보호구역 등에서 유사한 문제가 지속적으로 발생하고 있음.
+이에 대한 개선 방안으로
+무단 방치 행위가 3회 적발될 경우 이용자에게 과태료를 부과하고 서울시 내 공유 기기 이용을 영구 제한하는 ‘이용자 3OUT 제도’를 도입함
+으로써 이용자 책임을 강화하고자 함. 또한
+시민이 직접 방치된 기기를 지정 주차 구역으로 이동할 경우 건당 보상금(서울페이 등)을 지급하는 시민 참여형 견인 제도를 도입함
+으로써, 행정 인력이 미치기 어려운 골목 지역까지 실시간 정비가 가능하도록 함. 아울러
+해당 내용을 공유 기기 업체와의 협약 및 서울시 조례에 명문화하여 업체의 이용자 관리 책임을 강화하고 시민 참여형 정비가 가능하도록 행정적 기반을 마련함
+.
+이를 통해
+어린이 보호구역 내 보행 안전을 확보하고 도시 미관을 개선할 수 있을 것으로 기대됨
+. 더불어
+시민 참여를 통해 한정된 단속 인력을 보완함으로써 행정 비용을 절감하고, 지역 내 소득 창출과 선진적인 주차 문화 정착에 기여할 수 있을 것으로 판단됨
+.</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1549,10 +1869,8 @@
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="E14" t="n">
+        <v>2026</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -1611,6 +1929,31 @@
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>서울형키즈카페를 서울 생활권자 다자녀가족도 무료로 이용할 수 있도록 개선 부탁드립니다.
+서울생활권자는 사실상:
+？ 아이 유치원·학교 서울
+？ 부모 직장 서울
+？ 소비·교통·병원·문화생활 전부 서울
+？ 서울 혼잡·비용·육아환경 부담 똑같이 감당
+그런데도
+？ 주소지 한 줄 때문에
+？ 다자녀여도
+？ 무료 혜택 제외
+？？ 부담은 같이 지는데, 혜택만 못 받는 구조
+이게 억울한 포인트예요.
+솔직한 결론
+？ 공정하지 않음
+？ 육아 현실을 반영하지 못함
+？ 다자녀 정책 취지에도 어긋남</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1633,10 +1976,8 @@
           <t>2026-01-09</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="E15" t="n">
+        <v>2026</v>
       </c>
       <c r="F15" t="n">
         <v>57</v>
@@ -1695,6 +2036,17 @@
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>장위1동에 있던 작은 육아공간마저 사라지고 장위동 일대에 서울형 키즈카페가 아예 없어 장위동 아이들은 자차나 버스를 타고 다른 동이나 구로 이동하여 서울형 키즈카페를 가야하는 불편 함이 있습니다.
+장위동 일대에 많은 아파트가 들어서고 들어설 예정이니 많은 아이들이 찾을수 있는 서울형 키즈카페를 만들어 주셨으면 좋겠습니다.</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1717,10 +2069,8 @@
           <t>2026-01-04</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="E16" t="n">
+        <v>2026</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1779,6 +2129,17 @@
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>종로구는 혜명 놀이터만 있는데
+연령이 높아 다른 지역에 비해 이용이 불편한거 같습니다. 요즘 지역별로 멋지게 많이 짓던데 종로구도 하나 생겼으면 좋겠습니다~^^</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1801,10 +2162,8 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E17" t="n">
+        <v>2025</v>
       </c>
       <c r="F17" t="n">
         <v>3</v>
@@ -1863,6 +2222,19 @@
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>서울형 키즈카페 너무 만족스럽습니다
+요즘 조금씩 더 많은지역에 생기는것 같은데
+천왕역(7호선) 근처에도 하나 만들어주세요
+이용할 사람 은근 많아요</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1885,10 +2257,8 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E18" t="n">
+        <v>2025</v>
       </c>
       <c r="F18" t="n">
         <v>106</v>
@@ -1947,6 +2317,31 @@
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>서울 강서구 화곡동에 위치한 우장산 숲 아이파크에 거주 하는 주민입니다. 현재 이 아파트의 초등학교 배정 학교는 화곡초등학교입니다.
+이 학교는 현재 공사 중이라 당분 간 신월초등학교로 이전하여 학업 중에 있는 것으로 알고 있습니다.
+문제는 아파트에서 화곡초로 가기 위해서는 차량이 지나가는 좁은 골목길을 지나 화곡로라는 큰 길을 건너 다시 차량이 지나가는 골목길로 더 들어가야 학교 정문이 나옵니다.
+이러한 동선은 아이들이 안전하게 등하교를 할수 없는 매우 위험한 상황이라고 보입니다. 특히 빠른 배달 처리를 위해 쌩쌩 달리는 오토바이 기사들을 볼 때면 불안과 우려가 증폭 시킬 뿐더러 더욱이 신월초는 강서로와 화곡로 두 큰 길을 건너가야 되고 화곡역 번화가와 가까워 아이들의 정서에 이롭지 못한 분위기가 있습니다.
+또한 강서힐스테이트 134동 앞 게이트에서 우장초등학교 정문까지 500m정도 밖에 안되는데 셔틀버스타고 다니는 반면 우장산숲아이파크 후문에서 화곡초등학교 정문까지 600m가 넘어가고 신월초등학교 정문까지 900m가 넘는데도 걸어서 등하교를 해야하는 형평성 부분에서 문제가 발생하고 있습니다.
+이러한 점을 감안하여 배정 문제에 대한 해결이 필요해 보입니다.
+개선 방안을 3가지로 만들 수 있습니다.
+1. 셔틀버스가 다니는 우장초등학교로 배정학교를 변경한다.
+2. 신월초나 화곡초에 셔틀버스를 운행한다.
+3. 현재 오랫동안 공실 중인 윤희유치원 건물을 화곡초 분교로 만든다.
+윤희유치원 건물은 사유지이긴 하나 오랬동안 공실로 방치하고 있어 사용하는 방안에 대해 건물주와 협의는 충분히 만들어 낼수 있지 않을까 봅니다.
+현 정부에 들어 중대재해처벌법으로 근로자들의 안전을 강화하는 조치가 시행 되는 사례가 생겨나고 있습니다. 반면 저출산으로 인해 아이들의 귀해지는 현 시대에 무관심으로 일관하는지 모르겠습니다.
+심지어 작년에 도로 폭, 단지와 학교, 차선 갯수 횡단보도 건너는 횟수까지 적어서 민원 넣었는데 돌아온 답변은 8차선 도로 2번 건너는게 2차선 도로 1번 건너는것 보다 안전하다는 답변을 받은
+사례도 있습니다.
+어린 생명이 위협받는 중대한 사안에 대해 이러한 시대착오적인 잘못된 고정관념으로 인해 요청을 거부하거나 단순하게 처리하는 일이 있어서는 절대 안됩니다.
+아이들이 차량이 지나가는 좁은 골목길을 걷고 큰 길을 횡단하지 않는 방향으로 맞벌이를 하는 부모님이 고생하면서 픽하지 않고 안심하게 혼자서 안전한 등하교를 할수 있는 그런 개정이 절실히 필요하며 첨부파일을 첨부하오니 확인하시고 서울시 교육청과 함께 실사를 진행해 빠르게 추진해주시면 좋겠습니다.</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1969,10 +2364,8 @@
           <t>2025-09-18</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E19" t="n">
+        <v>2025</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
@@ -2031,6 +2424,18 @@
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>청약시 영유아 자녀에 한해 가산점을 주고 있으나 영유아에 대한 가산점처럼  자녀수에 대한 가산점이 확대 되었으면 합니다.
+예)자녀당 +5가 아니라
+1자녀시 5점,  2자녀시 10+5점, 3자녀시 15+10 점 같이 자녀수에 따른 청약시 가산점이 큰폭으로 늘어나가는 것을 제안하고 싶습니다.</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2053,10 +2458,8 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E20" t="n">
+        <v>2025</v>
       </c>
       <c r="F20" t="n">
         <v>2</v>
@@ -2115,6 +2518,20 @@
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>서울형키즈카페를 잘 이용하고있는 아기엄마 입니다~
+안전상의 문제로 키즈카페에 연령제한이 있는걸로 알고있는데요,
+3세 이상부터 가능한 키즈카페는 보통 오전에는 아이들이 어린이집에 가서 카페에 잘 없는것 같더라구요.
+집 바로앞에 보라매공원 서울형키즈카페가 새로 오픈했는데 보니까 3세 이상이여서
+17개월인 우리아기는 가까워도 이용을 못해서 좀 아쉽더라고요. 둘째 임신중이라 멀리 나가기가 힘들어서 가까운데 생겨 좋았는데, 큰 아이들이 어린이집에 가있는 오전시간에만이라도 서울형키즈카페를 사용할수있게 요청드리고 싶습니다.</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2137,10 +2554,8 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E21" t="n">
+        <v>2025</v>
       </c>
       <c r="F21" t="n">
         <v>69</v>
@@ -2199,6 +2614,21 @@
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>서울형가사서비스 종사자입니다.
+지난 7월 3일 영등포구의 "이주 노동자 생수나눔 &amp; 좋은돌봄 캠페인"에서 만난 가사노동자분께서 지난 6월에 영등포구의 돌봄종사자를 위해 백일해 무료예방접종을 실시하였다는 말을 들었습니다.
+서울형가사서비스는 임산부, 신생아, 18세이하 청소년가정에 가사스비스를 하는 일로 가족구성원과 직접 대면하기 때문에 만약 가사관리사가 약간의 기침만 해도 부모들은 불편해하고 서비스받기를 꺼려합니다.
+또한 가사노동자들 대부분은 경제적으로 여유가 없고, 고령의 노동자가라 취약한 건강조건을 가지고 있어서 독감등 호흡기 질환에 쉽게 노출되기도합니다.
+가정내 돌봄종사자 (가사관리사, 장애인활동지원사, 아이돌보미, 산후관리사, 생활지원사, 요양보호사 등)에게 독감, 백일해등 유행성 전염병에 대한 무료 예방접종을 희망합니다.
+가정내 돌봄 지원시 최우선 시행되어야 하는 일이라고 생각합니다.</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2221,10 +2651,8 @@
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E22" t="n">
+        <v>2025</v>
       </c>
       <c r="F22" t="n">
         <v>2</v>
@@ -2283,6 +2711,37 @@
         </is>
       </c>
       <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>안녕하세요.
+서울 시민 중 한 사람이자 한 아이의 아빠 입니다.
+길을 지나다니다 보면 어린이 보호 구역 내지는 노인 보호 구역 등에서
+30km/h 또는 50km/h의 속도 제한이 있긴 하지만 이 또한 카메라 단속 구간에서만
+규정 속도를 지키고 그 외 구간에서는 속도를 내는 일부 몰지각한 사람들이 더러 있습니다.
+또한 학교나 어린이집/유치원 등의 뒷골목 등의 좁은 길에는 단속 카메라 마저 없습니다.
+이런 곳에서 부주의 하게 과속 하는 운전자들을 많이 보게 됩니다.
+특히 택배와 배달이 난무하는 대한민국 서울특별시 에서는 더더욱 많이 보입니다.
+특정 구간에만 설치되어 있는 단속 카메라로 이들을 말리기엔 부족해 보입니다.
+차라리 공사 구간 또는 고속도로 터널 진출입로 등 처럼 바닥을 오목 하게 교차하여 파던지
+-&gt; [凹凹凹凹凹凹凹凹凹凹(오목 요) 형태]
+그게 아니라면 과속방지턱을 현 형태의 큰 모양이 아니라 작은 돌기 형태로 구간 내에 길게 설치 하여
+속도를 내어 달리면 차량이 심하게 흔들거리게 되어 속도를 내기가 힘들게 만들어 버리는 게 어떨까 합니다.
+-&gt; [△△△△△△△△△△(볼록 철) 형태]
+(-볼록 철 자가 금칙어 요건에 들어가서 등록이 안되네요...손가락 욕 같아서 인가요...)
+아이를 키우고 있는 입장에서 저출산 때문에 문제가 커지고 있는 대한민국의 현재라면
+비용이 문제가 되어서 못하는 부분은 아니라고 생각이 됩니다.
+부디 아이디어를 적극 활용 해주셔서 대한민국의 미래인 아이들이
+좀 더 살기 좋고 좀 더 건강하게 자랄 수 있도록 해주세요.
+피해를 입는 아이들이 여러분들의 아이이자 가족 일수도 있고 핏줄 일수도 있습니다.
+보다 나은 대한민국을 위해 간곡히 부탁 드립니다.
+긴 글 읽어 주셔서 감사합니다.</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2305,10 +2764,8 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E23" t="n">
+        <v>2025</v>
       </c>
       <c r="F23" t="n">
         <v>2</v>
@@ -2367,6 +2824,17 @@
         </is>
       </c>
       <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>서울형키즈카페를 자주 이용하는 아이엄마입니다. 날씨가 더워지면서 양말 착용없이 서울형키즈카페를 오시는 보호자들이 많이 보이는데요. 양말착용의무에 대해 잘 모르시는 거 같기도하고. 주변에 양말 구입할 곳이 없기도 하고. 이미 키즈카페 입구까지 온 상황에서 보호자와 직원들 모두 난감한 듯한 상황을 여러번 보았습니다. 키즈카페에서 구비해둔 아이들 임시슬리퍼 같은 걸 대여해주는 것을 본적이 있는데요. 보호자들은 실내슬리퍼를 빌려주시는 거 같더라고요.
+키즈카페 내 위생 및 양말 착용에 주의를 가질 수 있도록 소정의 금액(천원정도)을 받고 양말을 판매하시는 건 어떤지 건의드립니다. 그러면 키즈카페 내 직원들도 양말없이 방문한 가족에게 양말 착용의무에 대해 재설명하고 양말을 현장서 구입해 신고 입장할 수 있도록 하는는 게 좋을 거 같다는 생각이 듭니다.</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2389,10 +2857,8 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E24" t="n">
+        <v>2025</v>
       </c>
       <c r="F24" t="n">
         <v>4</v>
@@ -2451,6 +2917,21 @@
         </is>
       </c>
       <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>현황 및 문제점
+현재 어린이보호구역 중 초등학교정문앞도로 제외 모든 불법주정차구역에서는 24시간동안 운영되고있으나 어린이보호구역 중 초등학교정문앞도로는시간이 제한되어 있어 시간외에는 정차해도 주민신고제에 의한 과태료 부과가 안된다는 문제가 있다
+개선방안
+불법주정차 구역중 어린이보호구역 중 초등학교정문앞도로 시간 제한 폐지한다
+기대효과
+어린이보호구역 중 초등학교정문앞도로 시간 이후에도 단속강화로 어린이보호구역 중 초등학교정문앞도로 주정차 근절</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2473,10 +2954,8 @@
           <t>2025-04-28</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E25" t="n">
+        <v>2025</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2535,6 +3014,16 @@
         </is>
       </c>
       <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>공휴일이나 임시공휴일도 운영하면 좋겠습니다.</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2557,10 +3046,8 @@
           <t>2025-04-05</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E26" t="n">
+        <v>2025</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -2619,6 +3106,25 @@
         </is>
       </c>
       <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>현황 및 문제점
+교육이 가장 필요한 어린이들이 체험관에 직접 방문하여 이용하기는 어려우니
+체험교육장비가 장착된 이동형 안전체험버스를 제작하여 어린이집으로 직접 방문하여 어린이들이 안전교육을 받을 수 있게 되면 안전사고를 더 효과적으로 예방할 수 있을 것 같음
+또한 교육시설은 전 연령이 함께 이용할 수 있도록 제작하기 보다는 차량 내 갇힘사고 시 대응요령 등 어린이들에게 특화된 안전체험으로 제작하였으면 좋겠음
+개선방안
+이동형 안전체험버스 제작 및 운영
+- 차량 내 체험장비 : 어린이가 차량에 갇혔을 때 행동요령 체험공간, 화재 및 전기 안전 등 체험공간, 영상교육장치 등
+(그 외 어린이에게 특화된 체험공간)
+기대효과
+공간에 제약을 받지 않고 교육을 받을 수 있어 이동이 어려운 안전취약계층의 위급상황 대처능력 제고</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2641,10 +3147,8 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E27" t="n">
+        <v>2025</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
@@ -2703,6 +3207,27 @@
         </is>
       </c>
       <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>현황 및 문제점
+---
+‘가족 인증’의 목적은 보호자에게 어린이 안전 보호 책임을 부여하는 데 있습니다. 법적, 정서적으로 밀접한 부모가 어린이 안전모 착용, 자전거 이상점검 등의 지도감독 의무를 성실히 이행할 것이라고 판단하여 보호자의 범위를 부모로 한정한 점 이해하여 주시기 바랍니다.
+---
+다만 부모 중에 법적으로 어린이 안전 보호 책임을 부여를 못하는 사람들도 있습니다.
+또한 부모가 아닌 아이의 후견인은 법적으로 어린이 안전 보호 책임을 질 수 있지만 후견인의 책임으로 따릉이를 대여할 수 없습니다.
+개선방안
+1. 행정안전부의 실시간정보유통시스템을 활용하여 부모의 후견등기사항부존재증명서(전체)를 발급하여 각각의 부모에 대한 후견인이 존재하지 않는 사람만 어린이 안전 보호 책임을 부여를 할 수 있도록 합니다.
+2. 대상 어린이의 후견등기사항증명서(현재)를 조회하여 이 어린이의 후견인이 따릉이를 대여할 수 있도록 합니다.
+기대효과
+1. 자격이 없는 부모는 따릉이에 대한 어린이 안전 보호 책임자가 되지 않도록 합니다.
+2. 자격있는 후견인이 따릉이에 대한 어린이 안전 보호 책임자가 될 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2725,10 +3250,8 @@
           <t>2025-03-22</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E28" t="n">
+        <v>2025</v>
       </c>
       <c r="F28" t="n">
         <v>5</v>
@@ -2787,6 +3310,18 @@
         </is>
       </c>
       <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>안녕하세요.어린이들과 청소년을위한 공간..
+난나..청소년센터에대해 규제철폐를 요청합니다
+한부모.저소득아이들을위해 저렴하게..혹은 무상으로 아이들운동과 예술분야늘 배울수있는 좋은공간이라고생각하는데요..초1부터 여러가지배울수 있다는 장점이있는반면 혜택을받으려면 만9세가 넘어야한다는데..3학년이지만  12월생인 아이들은 만9세가 되지않는다는 이유로 혜택을못받고 전액수강료를 지급해야만 된다는데요..초1..학교를 다니고있다면 혜택을받을수있게 규제를 바꿔주시길바랍니다</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2809,10 +3344,8 @@
           <t>2025-03-21</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E29" t="n">
+        <v>2025</v>
       </c>
       <c r="F29" t="n">
         <v>1</v>
@@ -2871,6 +3404,22 @@
         </is>
       </c>
       <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>？
+？안녕하세요~^^
+저는 율현초에서 근무하는 어린이교통안전지도사입니다~
+서울시 강남구 율현동 율현초등학교 후문 앞은 작은 이차도로 입니다
+그런데 이곳이 신호가 없고 지름길이다보니 어린이안전보호구역인데도 대부분 과속으로 차들이 운전을 합니다
+특히나 아이들이 이곳을 지나 학교에 등교를 하는데 상가에서 나오는 차량과 이차도로에 오고가는 차량으로 등교길이 매우 위험하고 오늘도 출근시간에 과속하던 차량 사고가 바로 학생들이 들어오는 후문 앞에서 있었고 다행히 아이들 등교시간 전이라 인명사고는 없었지만 매일매일이 아이들한텐 사고의 위험이 도사리고 있는곳입니다
+더 큰 사고가 일어나기 전에 학교 후문에 과속방지카메라를 달아주시어 학부님과 학생들이 좀 더 안심하고 안전하게 등교할 수 있도록 부탁드립니다</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2893,10 +3442,8 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E30" t="n">
+        <v>2025</v>
       </c>
       <c r="F30" t="n">
         <v>102</v>
@@ -2955,6 +3502,29 @@
         </is>
       </c>
       <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>안녕하세요. 노고가 많으십니다.
+첫번째로 마포구의 용강초등학교 등굣길을 개선 제안하고자 글을 올립니다.
+학교로 진입하는 길 중 백범로17길과 대흥로20안길이 있는데 백범로17길은 어린이 보호구역으로 지정이 되어 있고 대흥로 20안길은 지정이 안되어 있어. 학교로 등교하는 모든 길이 안전한 등굣길로 개선되고자 제안을 합니다.
+똑같이 학교로 진입하는 길인데 차별을 두는건 안된다고 생각합니다. 어린이의 안전에는 차별이 없습니다.
+두번째로는  백범로17길은 어린이 안전구역이다 보니 불법주차가 거의 없는데 대흥로 20안길은 불법 주차로 아이들 등교와 출근하는 차와 맞물려 위험에 노출된 상태에서 불법 주차된 차량들로 좁은길이 더 좁아져 위험성이 더 높습니다.
+더군다나 양방향으로 차량이 다닐 수 있다보니 양쪽에서 챠랑이 오면 차는 물론이고 아이들 및 어른들도 어디로 피해야 할지 모르는 상황이 올 때가 많습니다. 이에 어린이 보호구역은 물론 일방통행 길로 지정을 하여 위험수위를 낮추고자 제안합니다.
+세번째로 주차로 주민들 간의 싸움이 있습니다. 혼자 불법 주차하겠다고 오토바이, 자전거, 배너 간판 등 여러 물건으로 자리를 차지한 다음 다른 차는 주정차를 못하게 막아 놓고 혹여나 다른 차가 잠시 주정차를 하고 있으면 당장 빼라고 싸웁니다. 근데 알고 보면 그 사람도 그 집 앞이나 그 동네 사는 사람이 아닙니다. 그리고 최근 빌라들도 몇 개 생겨 주차장이 있는 건물들이 생겼는데 이른 아침이나 늦은 밤 차량 입출차를 못해 차량 주인 찾는다고 큰소리로 차주를 찾는 경우도 있습니다.
+대흥로 20안길에 주차를 할 수 있게 그냥 두실거면 싸우지 않고, 주차장이 있는 차주들이 차량을 입출차 못하는 상황이 없게
+거주자우선주차 구역으로 몇 개 만들어 주셨으면 합니다. 벽에는 마포구청 이름으로 주차금지라고 쓰여 있는데 왜 어린이 보호구역이며, 일방통행, 주차단속을 안하는지 모르겠습니다.
+위험과 불편이 많은 대흥로20안길의 개선을 제안합니다. 용강초등학교에서도 학교 주변 길의 일방통행 학부모 의견 수렴을 했었습니다. 이는 아이들의 안전한 등교를 위함으로 여겨집니다.
+1. 어린이 보호구역 지정으로 아이들의 안전한 등굣길 확보
+2. 일방통행 지정으로 차량 및 사람 통행 보호 확보
+3. 거주자우선주차 지정으로 이웃간의 불화 해소 및 불편 해소
+이중 하나라도 이행해 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2977,10 +3547,8 @@
           <t>2025-03-12</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E31" t="n">
+        <v>2025</v>
       </c>
       <c r="F31" t="n">
         <v>2</v>
@@ -3039,6 +3607,16 @@
         </is>
       </c>
       <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>등하교 시간이 훨씬 지난 밤 9시부터 아침 8시에는 30키로라는 속도 제한을 풀어야한다고 봅니다. 백번 양보해서 밥ㅁ 10시부터 아침 7시라도 풀어서 귀가하거나 아침 일찍 출근 하는 사람에게 도움이 되는 정책이 필요해요. 왜 아이들이 다니지 않는 시간에도 속도제한을 두는 겁니까?</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3061,10 +3639,8 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E32" t="n">
+        <v>2025</v>
       </c>
       <c r="F32" t="n">
         <v>2</v>
@@ -3123,6 +3699,97 @@
         </is>
       </c>
       <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>스쿨존은 초등학교 정문을 중심으로
+300m
+이내의 도로에 자동차의 최대 속도를
+30km/h
+이내로 제한하고 있다
+.
+위반 속도에 따라 벌금이나 과태료를 부과받는다
+.
+교통사고의 위험으로부터 어린이를 보호하기 위하여 지정된 구역으로 필요성에 공감한다
+.
+전국의 모든 초등학교 앞 통학로에
+24
+시간 적용하는 것은 차량 운행자로서는 불합리한 면도 있다고 생각한다
+.
+등하교 시간엔 당연히 학생들의 이동이 많으므로 규정 속도를 지켜야 어린이들의 안전을 보장할 가능성이 크다
+.
+하지만 늦은 밤이나 새벽
+,
+인적이 드문 지방 도로나 오지조차도 초등학교가 있다고 같은 규정을 적용하는 것이 적절한지는 의문이다
+.
+코로나 팬데믹 시절
+,
+강원도 횡성의 오지 마을로 불리는 면 소재지에서 생활했다
+.
+그곳 역시 초등학교 인근에는 어린이보호구역으로 속도를 규제했다
+.
+학생 수가 교사보다 적은 지역이고
+,
+평소에도 이동 차량이 도시보다 상대적으로 적을 뿐 아니라 늦은 시간이나 새벽엔 인적은 물론 차량 통행이 거의 없다
+.
+그런데도 어린이보호구역을 통과할 때는 속도 제한 때문에 운행 시 주의가 필요하다
+.
+지난달
+,
+오랜만에 지인을 만나기 위해 그곳에 갔더니
+40km
+구간으로 변경한 것을 확인할 수 있었다
+.
+그렇게 변경할 수 있다면 지역의 차량 이동과 여건에 따라 탄력적으로 운영하는 것도 가능한 건 아닌가란 생각이 들었다
+.
+어린이보호구역의 필요성은 유지해야 하나 특정한 시간대에는 속도 제한을 탄력적으로 운영하는 것이 효율적이라 여긴다
+.
+예를 들면
+,
+등하교와 관련이 적은 밤
+9
+시부터 새벽
+6
+시
+,
+또는 저녁
+6
+시 이후부터 새벽
+7
+시까지
+,
+혹은 그 외 적절한 시간 동안에는 규정 속도를 시내 운행 속도처럼
+50km
+로 바꾸는 것이다
+.
+아파트 단지가 밀집된 도시의 주거지 근처에는 대부분 초등학교가 있기 마련이다
+.
+초등학교 품은 아파트
+(
+초품아
+)
+라고 불린 정도로 인기까지 높다
+.
+이런 곳은 출퇴근 시간에 차량이 더 많아진다
+.
+출근 시간은 등교 시간과 비슷할 수도 있지만
+,
+퇴근 시간은 대부분 학생이 많지 않다
+.
+그런데도 속도 제한 때문에 오히려 차량이 늘어나 막히는 현상마저 있다
+.
+갑자기 속도를 줄여야 하는 불편도 있어 자칫 속도위반 과태료 고지서를 받기 쉽다
+.
+도로는 보행자와 차량 운행자 모두를 보호해야 하므로 어린이 교통안전 교육과 더불어 시간대에 따라 탄력적으로 운행 속도를 조절하는 스쿨존이었으면 좋겠다
+.
+보행자인 어린이 보호의 취지와 함께 운전자의 운행 여건도 충분히 고려한 정책이었으면 좋겠다
+.</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3145,10 +3812,8 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E33" t="n">
+        <v>2025</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -3207,6 +3872,18 @@
         </is>
       </c>
       <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>어린이보호구역의 시간을 정하면 교통 체증의 해소에 도움이 될것으로 보입니다.
+어린이들의 이동 시간인 오전 8시~오후 8시까지 어린이보호구역 속도제한을 하되,
+그 이후 시간에는 일반 도로의 속도 제한이면 좋겠습니다.</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3229,10 +3906,8 @@
           <t>2025-02-18</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E34" t="n">
+        <v>2025</v>
       </c>
       <c r="F34" t="n">
         <v>3</v>
@@ -3291,6 +3966,21 @@
         </is>
       </c>
       <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>서울시 정책으로 여러 지역에 서울형키즈카페가 생겨서 아주 유용히 이용 하고 있음에 정말 감사드립니다
+하지만 이용가능 시간이 워킹맘들에겐 맞지 않아 제안드립니다
+보통 워킹맘들은 아이를 어린이집에 보내서 하원하러 가면 16:30분 정도 입니다
+하지만 서울형 키즈카페, 용산 꿈나무놀이터, 여러 박물관 등 의 평일 이용시간이 17:30분 까지 밖에 안되어 한시간도 채 이용을 못하는 경우가 많습니다
+18:00로 30분이라도 더 늘려 주시면 육아에 많은 도움이 될것 같습니다
+꼭좀 반영 부탁드립니다</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3313,10 +4003,8 @@
           <t>2025-02-17</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E35" t="n">
+        <v>2025</v>
       </c>
       <c r="F35" t="n">
         <v>3</v>
@@ -3375,6 +4063,24 @@
         </is>
       </c>
       <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>어린이 보호구역 속도 제한에 관해서
+어린이 보호구역 속도 제한에 동의하지만
+어린이를 보호하는 목적으로 생긴 속도제한이
+야간에도 이뤄지는게 맞는건가 싶은 생각을
+갖고있던 사람으로 제안 드립니다
+최소 00시부터 06시까지는 어린이 보호구역
+속도제한 단속이 해제 되어야된다고 생각합니다
+어린이 통학시간도 아니고 어린이들이 없는 시간까지 속도제한과 단속이 이뤄진다는게 주변학교가 많은곳에 사는 사람으로 매우 불편함을 느낍니다
+어린이 보호 목적은 좋지만 버스전용도로 단속과 같이 일정 시간에는 풀어주는것도 좋은거같습니다</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3397,10 +4103,8 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E36" t="n">
+        <v>2025</v>
       </c>
       <c r="F36" t="n">
         <v>4</v>
@@ -3459,6 +4163,18 @@
         </is>
       </c>
       <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>？어린이보호구역  자동차속도 제한
+일요일과 공휴일, 폐지 평일은
+오후 7시이후 부터 오전7까지 속도제한  풀어주실 수는 없는건지 건의 드립니다</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3481,10 +4197,8 @@
           <t>2025-02-07</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E37" t="n">
+        <v>2025</v>
       </c>
       <c r="F37" t="n">
         <v>3</v>
@@ -3543,6 +4257,16 @@
         </is>
       </c>
       <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>관악구 인헌초등학교 ~ 서울과학전시관까지 어린이 보호구역과 노인보호구역 지정뿐 아니라  서울시민대학 다시가는 캠퍼스 (구, 관악복합평생교육센터)로 인해 , 과속방지 후면 카메라 단속도 실시되어 30  50  속도로 차량이동이 이루어지고 있다. 인헌동 주민들도 낙성대 터널을 경유하여 서울대입구 지하철 방면으로 이동시에 통과하는 지역이고,  반대로 인헌동으로 가기 위해 거치는 도로인데 ,  주로 어린이 노인이 이용하는 평일 0900~1800을 제외한  시차제라도 도입해 주었으면 한다 (물론 단속을 다소 완화해 주면 더 좋겠지만 ？)</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3565,10 +4289,8 @@
           <t>2025-02-05</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E38" t="n">
+        <v>2025</v>
       </c>
       <c r="F38" t="n">
         <v>4</v>
@@ -3627,6 +4349,16 @@
         </is>
       </c>
       <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>어린이보호구역 시속30키로 규제를 심야시간과 주말,공휴일은 해제했으면 합니다</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3649,10 +4381,8 @@
           <t>2025-02-04</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E39" t="n">
+        <v>2025</v>
       </c>
       <c r="F39" t="n">
         <v>1</v>
@@ -3711,6 +4441,19 @@
         </is>
       </c>
       <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>어린이 보호구역 시간제 운영 제안합니다
+예를들면 저녁 9시 이후부터 익일 오전 6시까지 속도제한 해제 및 어린이보호구역 일시 해제
+새벽 한두시에 어린이집 앞 초등학교 앞 횡단보도 길건너는 아이들이 누가있다고..
+실효성에 대해 생각해봤으면 합니다</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3733,10 +4476,8 @@
           <t>2025-02-04</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E40" t="n">
+        <v>2025</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -3795,6 +4536,20 @@
         </is>
       </c>
       <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>최근 도서관을 자주 이용하게 되면서 불편한 점이 있어 개선 요청 드립니다.
+현재 도서관 회원에 가입 및 가족회원으로 등록히게 되면 가족이 같이 가지 않아도 깉이 빌릴 수 있게 되어있습니다.
+이는 너무 좋으나 홈페이지에서 검색했을때는 가족이 대여한 도서 목록은 함께 검색이 되지 않아 건건이 로그인을 해서 반납일 등을 확인해야하는 번거로움이 있습니다.
+가족회원으로 등록된 경우 한 아이디로 로그인시에도 타 가족의 도서 목록도 조회가 가능하도록 요청 드립니다.
+혹 가족간에도 목록 열람을 비공개 원할시에는 통합 조회여부에 대해 선택할 수 있도록 하면 하면 될듯 합니다.</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3817,10 +4572,8 @@
           <t>2025-02-03</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E41" t="n">
+        <v>2025</v>
       </c>
       <c r="F41" t="n">
         <v>85</v>
@@ -3879,6 +4632,21 @@
         </is>
       </c>
       <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>현재 sh공사에서 모집하는 구 역세권 청년주택 현 청년안심주택에서 반려동물 양육 및 출입금지를 주요 퇴거사항으로 기재해 놓고 있습니다.
+흡연이나 층간소음 등 기타 다른세대에 불편을 끼치는 사항은 당연히 금지되어야 하나 반려동물의 양육 심지어 출입까지 금지시키는 것은 시대착오적 규정이라고 생각합니다.
+해당규정때문에 기존에 반려동물을 양육중인 청년 또는 신혼부부는 입주를 포기하거나 파양하는 등 오히려 반려동물의 유기를 조장하고 있습니다.
+반려동물이 시설을 훼손하는 경우 퇴거시 복구의무를 부여하면 되는 것이지 원천금지하는 것은 과한 규정이라고 생각합니다.
+반려동물을 양육하는 세대가 갈수록 늘어나고 있는 만큼 관련규정도 다시 검토해주시길 부탁드립니다.
+감사합니다.</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3901,10 +4669,8 @@
           <t>2025-02-03</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E42" t="n">
+        <v>2025</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -3963,6 +4729,22 @@
         </is>
       </c>
       <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>？
+2023년 9월부터 서울시민 대상으로 조부모 돌봄수당이 시행되었습니다.
+맞벌이로 인해 조부모에게 실질적으로 양육을 의전헤야하는 서울시 양육자에게 꼭 필요한 사업이었고 이러한 정책이 약 10년만의 서울시 출생율을 올리는데 일조했다고 생각합니다!
+하지만 지원대상이 24-36개월로, 도움이 많이 필여하고 4시 30분을 어린이집 기존 하원시간으로 정해진
+36~48개월, 즉 법적 영아에게는 아무 지원이 없습니다!
+최소한 48개월 영아 또는 7세 미만의 미취학 영유아가 스스로 등하원을 할 수 없음을. 서울시에서 정책적으로 지원하기를 희망합니다!!
+이는 서울시의 출생율증가와 시니어에 대한 일자리 증가와 사회참여도 증가에 기여할 것입니다.</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3985,10 +4767,8 @@
           <t>2025-01-05</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E43" t="n">
+        <v>2025</v>
       </c>
       <c r="F43" t="n">
         <v>2</v>
@@ -4047,6 +4827,29 @@
         </is>
       </c>
       <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>근래 애완견을 기르는 인구가 폭발적으로 늘어나고 있습니다.
+그런데 주변분들에게 많은 피해를 주고 있습니다.
+본인은 사랑하는 애완견이지만
+개를 싫어하는 분들에게는 혐오물이 될 수 있습니다.
+1. 짖어서 소음
+2. 털이 빠져 날려서 호흡기 장애
+3. 주면에 냄새
+요즘 개를 데리고 운동시킨다며 다니는데
+개는 외출하면 습관적으로 소변으로 표시하는 버릇이 있습니다.
+어떤 때는 똥을 싸고 치우지도 않아 눈살을 찌푸리게 합니다.
+그래서 길거리나 공원 등에 냄새가 많이 납니다.
+그리고 병균을 옮길 수도 있습니다.
+그래서 캠페인을 해 주셨으면 합니다.
+애완견 외출시 기저귀를 채우자</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4069,10 +4872,8 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="E44" t="n">
+        <v>2024</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -4131,6 +4932,21 @@
         </is>
       </c>
       <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>현황 및 문제점
+아이들은 보통 안전을 위해 부모랑 같이 등교하는데  맞벌이 부부등은 아이랑 동행하는데 제약을 받는경우가 있어 간혹 혼자보내는 경우가 있을수 있는데 이런경우 아이들의 안전이 걱정될 우려가 있다는 문제가 있다
+개선방안
+초등학교 1~2학년을 대상으로 방향이 같은 8명 내의 아이들로 노선을 구성한 뒤 노선 당 1명의 지도사를 배치해 등 하굣길을 함께 한다
+기대효과
+맞벌이 부부등 아이랑 동행하기 어려운분들의 동행부담감 해소</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4153,10 +4969,8 @@
           <t>2024-10-15</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="E45" t="n">
+        <v>2024</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -4215,6 +5029,27 @@
         </is>
       </c>
       <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>안녕하세요.
+저는 서울시 노원구 월계동에 살고있는 두아이 아빠 입니다.
+바로드릴 말씀은 동네벽이 너무 낙후되어 뜯어지고 곰팡이에 절여져서 귀신동네가 되었습니다.
+특히 아이들이 친구들은 챙피하고 무서워서 친한친구들 초대도 못하고 특히 밤에는 나가지도 못하고 있습니다.
+배달로 먹고사는 아빠로서는 그져 미안한 마음만 느끼고 있습니다.
+건의 드리고져 하는 사항은 (노후된 벽을 좋은 그림을) 그려주셔서 성장하는 아이들에게 기분좋은 동네로 만들어 주세요.
+힘없는 동네 아버지가 인자하시고 힘있는 오세훈 서울시장 아버님께 간곡히 부탁드립니다.
+노후된 벽에 좋은 그림으로 우리 꿈나무들에게 희망을 주세요.
+이런 말씀드려서 안될줄 알지만 깨알같은 작은 희망으로 말씀드립니다.
+귀신동네 벽이 있는곳은
+(서울특별시 노원구 석계로 27-1  입니다.
+감사합니다. 늘 행복하세요.</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4237,10 +5072,8 @@
           <t>2024-10-07</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="E46" t="n">
+        <v>2024</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
@@ -4299,6 +5132,17 @@
         </is>
       </c>
       <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>어린이보호구역에 기존 녹색어머니나 시니어 외, 시에서 노인 일자리 제공 일환으로 수시로 관리감독하게 하면 좋겠습니다
+아이들의 안전도 지키고 노인 일자리도 생기고요</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4321,10 +5165,8 @@
           <t>2024-09-09</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="E47" t="n">
+        <v>2024</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -4383,6 +5225,20 @@
         </is>
       </c>
       <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>1. 현재상황
+현행 어린이보호구역 및 동종지역(이하 '어린이보호구역등') 내 차량속도는 30km이하로 제한되어 있고 단속을 하고 있는 실정입니다.
+그 외 대부분의 도심지 차량속도는 50km이하로 제한되어 있고 단속을 하고 있습니다. 이러한 속도제한과 단속은 모두 교통사고 예방에 큰 역할을 하고 있는 좋은 규제입니다. 다만, 야심한 때, 공휴일에도 천편일율적으로 그대로 적용하는 것은 교통흐름에지장을 초래하는 불편으로 시민들의 불만이 큰 것도 현실입니다.
+2. 제안사항
+어린이보호구역등의 제한속도를 하교시간 이후인 18시 이후부터 심야시간대, 토요일 오후시간부터 심야시간대, 그리고 공휴일에는 도심지 제한속도인 50km로 탄력운영할 수 있도록 조정하여 주시길 제안합니다. 도심지내 제한속도인 50mk 정도면 상당히 안전한 속도로 볼 수 있으므로 시민불편을 최소화하는 방안으로써 적극 검토하여 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4405,10 +5261,8 @@
           <t>2024-08-26</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="E48" t="n">
+        <v>2024</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -4467,6 +5321,19 @@
         </is>
       </c>
       <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>수업 내용은 정말 유익했고, 선생님도 두분이셔서 수업 진행도 매우 매끄럽고 좋았습니다.
+다만 만남의 장소를 좀 더 자세하게 공지해주시면 좋을 거 같습니다. 초행길에 공원에서 좀 찾아다니게 되더라구요.
+또한 공원에 주차할 곳이 없는데, 주변 세곡문화센터 토요일 주차(유료) 가능한 점도 같이 안내해주시면 예약하는데 도움이 될거 같습니다.
+즐거운 체험 감사했습니다.</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4489,10 +5356,8 @@
           <t>2024-08-13</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="E49" t="n">
+        <v>2024</v>
       </c>
       <c r="F49" t="n">
         <v>19</v>
@@ -4551,6 +5416,96 @@
         </is>
       </c>
       <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>존경하는 오세훈 시장님 안녕하십니까
+,
+저는 아이의 아버지이자 신혼부부인 한 사람입니다
+.
+저는 동작구 사당
+1
+동에 작은 빌라 하나를 가지고 있습니다
+.
+저는 어릴때부터 아이를 많이 가지는 것이 꿈이었습니다
+.
+하지만
+,
+서울의 집값이 너무 비싸고 지금 소유한 빌라의 여건 상
+,
+여러 아이에 부모님까지 모시고 살기에는 너무 작은 집이기에 그 꿈을 포기할 수 밖에 없었습니다
+.
+게다가
+,
+우리 사당
+1
+동은 차량이 지나다니기에도 길이 좁고 아이들이 뛰어놀기에도 위험하며
+,
+특히
+'22
+년을 포함하여 장마철에 자주 물에 잠기는 침수 지역으로 아이들을 마음 놓고 안전하게 키우기에는 많은 어려움이 있었습니다
+.
+이에 저는 저의 빌라가 넓고 안전한 아파트단지로 탈바꿈하여 아이를 많이 낳고 우리 아이들을 안전하게 차량 걱정 없이
+,
+수해 걱정 없이 키우려는 큰 꿈을 안고 우리 사당
+1
+동 사당
+15
+구역 신속통합구역에 대한 찬성표를 던졌습니다
+.
+우리 구역은 이번 부동산 대책으로 인한 용적률
+330%
+적용 시 조합원 이외에
+1,000
+세대 이상 일반분양이 가능하여 현재 공급 부족으로 천정부지로 치솟고 있는 서울시의 집값 안정화에도 일정부분 기여를 할 것이며
+,
+이는 시장님의
+'
+공급 확대를 통한 부동산 가격 안정화
+'
+라는 생각과도 일치합니다
+.
+하지만
+,
+우리 구역 내 신속통합 반대파
+13%
+들은 자신들이 원주민이고 빌라 소유자들로
+'
+사업성이 떨어진다
+'
+라는 계산으로 우리 구역 내의 순수한 찬성 주민
+60%
+의 의도를 왜곡하며 절대 소수임에도 우리 구역의 지정을 막고 있습니다
+.
+그들의 왜곡과 다르게, 빌라 소유주들은 소위 '거지'가 아니며 분담금을 부담하고 정당하게 새로운 아파트를 얻게 될 것입니다.
+사당
+1
+동은 그들만의 것이 아닌
+,
+구역민 전체의 것이고 나아가 재개발 후 새로 사당동에 살게 될 새로운 주민들과 우리 미래 세대 모두의 것이기도 합니다
+.
+저는 오늘도 현재 구역민과 새로 분양받아 입주하는 새로운 주민들
+,
+그리고 임대 혜택에 의해 더불어 살게될 주민들이 모두 함께 안전하고 수해와 차량사고 걱정없이 살아가는
+4,000
+세대의 새로운 사당
+1
+동을 꿈꿉니다
+.
+부디 저와 우리 구역민들의 간절한 소원과 같이 서울 핵심지인 우리 사당
+1
+동에
+1,000
+세대 이상 고품질 주거공간 추가 공급과 우리 아이들의 미래를 위한 안전한 터전을 위한 사당
+15
+구역 지정과 신속한 추진을 부탁드립니다
+.</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4573,10 +5528,8 @@
           <t>2024-08-09</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="E50" t="n">
+        <v>2024</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -4635,6 +5588,19 @@
         </is>
       </c>
       <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>키즈카페애 수용인원이 점점 늘어나요
+부모님들 까지 오면 100명입니다
+안전사고 걱정됩니다
+아직 어린아기들이 오는 곳인데 감염 위험도요 수</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4657,10 +5623,8 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="E51" t="n">
+        <v>2024</v>
       </c>
       <c r="F51" t="n">
         <v>1</v>
@@ -4719,6 +5683,23 @@
         </is>
       </c>
       <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>현황)
+어린이 보호구역에서의 사고는 많이 일어나고 있습니다. 특히 운전자의 입장에서는 어린이 보호구역인지도 모르고 운전하는 경우가 많았습니다. 지금은 그나마 경찰청에서는 운전자가 어린이 보호구역에 진입했다는 것을 알수 있도록 어린이 보호구역이 시작되는 지점에는 기점 표시, 끝나는 지점에는 종점 표시를 아스팔트에 그리고 있습니다. 그런데 이게 실효성이 있을까요?
+좀 더 눈에 확 들어오게 할 필요가 있습니다.
+개선방안)
+어린이 보호 구역 시점과 종점 바닥 그리고 어린이 보호구역에 있는 방호 울타리를 노란색으로 칠하는 것입니다. 그러면 운전자의 입장에서는 어린이 보호구역에 진입했다는 것을 확실하게 알 수 있습니다. 어린이 보호구역에서 사고를 낸 운전자의 대부분은 자신이 어린이 보호구역에 진입했는지 몰랐다고 합니다. 그렇다면 어린이 보호 구역 시점과 종점 바닥 그리고 어린이 보호구역에 있는 방호 울타리를 노란색으로 칠해서 온통 주변이 노란색으로 만들면 될 것입니다. 주변이 온통 노란색인데, 누가 속도를 높일까요?
+도색비용이 많이 들 것을 우려하겠지만, 그 비용으로 어린이의 생명을 구하거나 부상을 예방할 수 있다면 세금이 효율적으로 사용되는 것이라 생각됩니다.
+기대효과)
+어린이 보호 구역 시점과 종점 바닥 그리고 어린이 보호구역에 있는 방호 울타리를 노란색으로 칠하면 어린이 보호구역에서 사고를 낸 운전자의 대부분은 자신이 어린이 보호구역에 진입했는지 몰랐다고 하는 변명이 통하지 않을 것입니다. 그리고 그 보다도 어린이 보호구역에 진입을 인지하고 나서부터는 운전자들이 더 조심해서 운전할 것이고, 어린이 보호구역에서의 사고는 더 줄어들 것 입니다.</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4741,10 +5722,8 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="E52" t="n">
+        <v>2024</v>
       </c>
       <c r="F52" t="n">
         <v>1</v>
@@ -4803,6 +5782,17 @@
         </is>
       </c>
       <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>？양천구 기준으로, 장난감 도서관 및 공동육아방은 소독시간이 있습니다.
+하지만, 코로나 등 전염병이 있지 않은 상황에서 소독시간이 꼭 필요한지 확인이 필요할거같습니다. 다른 도서관 등에 비해 이용객이 많지도 않은데 소독시간에는 문을 걸어잠궈 방문시 기다린적이 있습니다. 안에서는 실질적으로 소독이 아닌 휴식을 취하시고 계시더라고요. 다른 도서관이나 공무원분들하고의 형평성에 맞지않을뿐더러 어른에 비해 컨디션 관리가 어려운 아이들에게 점심시간에 오후소독시간까지 피해서 방문하려니 남는시간이 적게만 느껴집니다. 출산률 저조 등으로 이용객이 줄어드는데 꼭 중간에 휴식 시간을 만들어야하는지 고민이 필요한거 같습니다. 기타 성인 도서관에 준하여 운영시간을 동일하게 하는게 맞을거 같습니다.</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4825,10 +5815,8 @@
           <t>2024-06-30</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="E53" t="n">
+        <v>2024</v>
       </c>
       <c r="F53" t="n">
         <v>14</v>
@@ -4887,6 +5875,16 @@
         </is>
       </c>
       <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>안녕하세요? 7세 자폐성 장애를 가진 조카가 있습니다. 4세부터 장애를 알게 되었고 서울형 키즈카페를 여러군데, 여러번 이용해보았습니다. 저렴한 가격으로 깨끗하고 안전한 시설들로만 잘 꾸며져서 아이들이 이용하기 좋았습니다. 하지만 상대적으로 소통이 어렵고 질서 지키기가 잘 안되는 장애 아이의 특성상 일반 아이들과 같은 공간에서 놀기에 어려운점이 많습니다. 상주직원들의 장애아에 대한 이해도 부족합니다. 일반 아이들과 부모들과 직원들의 눈치를 보지 않고 장애아이들과 부모들이 좀더 즐겁고 마음 편하게 시간을 보낼 수 있는 장애아들만을 위한 서울형 키즈카페를 만들어주셨으면 좋겠습니다. 감각통합 놀잇감과 장애아의 특성을 이해해줄수 있는 상주직원들도 있으면 좋을거 같습니다.</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4909,10 +5907,8 @@
           <t>2024-06-20</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="E54" t="n">
+        <v>2024</v>
       </c>
       <c r="F54" t="n">
         <v>1</v>
@@ -4971,6 +5967,18 @@
         </is>
       </c>
       <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>한국 고등학생들은 평일에 학교와 학원을 오가며 하루 평균 10시간 이상을 교육기관에서 보내고 있습니다. 학교 수업 이후 추가적인 학습을 위해 학원까지 다니는 생활 패턴은 고등학생들에게 극도의 스트레스와 피로감을 유발합니다. 학업 외적으로도 학생들의 생활 품질과 안전을 저해하는 요소를 개선하기 위해 지방자치단체 고유의 고등학생 하원 택시 운영제도 운영을 제안합니다.
+학원이 끝나는 오후 9시~11시에는 택시 이용자가 소속학교 인증을 통해 학생임을 인증할 경우 지방자치단체가 적용한 저렴한 택시 요금으로 집까지 하원할 수 있게 하는겁니다. 또, 학생 혼자 택시를 타면 위험에 노출되기 쉽다는 문제를 해결하기 위해 생각한 방안으로는 해당 옵션의 택시 기사는 엄격한 운전자 선발 과정을 통과해야 하게 하는 것이 있습니다. 또는 자율주행자동차 기술을 이 정책에 활용하면 가장 좋을 것 같습니다.
+학생들이 안전한 교통 이동을 보장받아 스트레스와 피로감을 줄일 수 있다는 가장 큰 장점이 있고, 학생들과 학부모들의 시간 관리 및 생활 편의성이 향상될 것입니다. 또, 공공 교통의 활용도가 높아지면서 개인 차량 운행으로 인한 환경 부담을 줄 일 수도 있습니다. 최종적으로는 혁신적인 교통 정책 도입으로 인해 지방자치단체의 이미지와 사회적 신뢰도가 향상될 것을 기대할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4993,10 +6001,8 @@
           <t>2024-03-18</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="E55" t="n">
+        <v>2024</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -5055,6 +6061,24 @@
         </is>
       </c>
       <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>진짜 요즘에 스쿨존에서 크고 작은  아이들 교통사고가
+교통단속과 단속카메라, 과속방지턱 등
+차량의 안전운전을 위한 방안들도 중요하지만
+최소한의 이동중에는 사용을 조금 제안 하여
+안전에 좀더 신경쓸수 있도록
+서울강서초등학교 앞에도 설치 부탁드립니다!!
+민식이 법으로 운전자들도 힘듭니다
+꼭 시행됐으면 좋겠습니다
+스쿨존 보행안전 지킴이!! 가즈아</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5077,10 +6101,8 @@
           <t>2023-10-15</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="E56" t="n">
+        <v>2023</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -5139,6 +6161,17 @@
         </is>
       </c>
       <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>어린이 보호구역에서의 횡단보도 건널목은
+시인성과 경계심을 높히기 위해 노란색을 적용하였으면 합니다.</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5161,10 +6194,8 @@
           <t>2023-10-04</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="E57" t="n">
+        <v>2023</v>
       </c>
       <c r="F57" t="n">
         <v>18</v>
@@ -5223,6 +6254,69 @@
         </is>
       </c>
       <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>1.
+현황
+최근 어린이보호구역내 교통사고 증가로 인하여 교통사고 발생을 미연에 방지해야 할 필요성 대두
+2.
+개선방법
+가
+.
+횡단보도의 설치변경
+(
+높이
+)
+을 통한 교통사고 예방
+-
+현재 어린이보호구역내 횡단보도의 경우 일반지역의 횡단보도와 똑같은 규격으로 설치되어 있음
+이에 어린이보호구역내 특히 이면도로에 국한하여 횡단보도 설치를 변경 설치하여 교통사고를
+미연에 방지
+-
+보통 차량의 경우 과속방지턱 앞에서는 서행을 할수밖에 없음
+.
+이를 착안하여 어린이보호구역내
+횡단보도 설치시과속방지턱 기능을 추가시켜 도로면보도 높게 횡단보도를 설치 함
+.
+-
+기존 과속방지턱
++
+횡단보도
+=
+과속방지턱 높이로 횡단보도 설치
+나
+.
+어린이보호구역 내 일부 구역
+(
+경사진 도로면
+,
+교통사고 위험이 상존하는 구역 등
+)
+화물 승하차
+일시 금지조치
+-
+어린이보호구역내 아이들 틍하교 시간 등에 화물차의 화물 승하차를 일시 금지조치하여 어린이
+교통사고를 미연에 방지
+3.
+기대효과
+가
+.
+횡단보도를 과속방치턱처럼 높이 설치함으로써 차량의 일시정지를 유도 사전에 교통사고 방지
+효과과 클것으로 판단됨
+나
+.
+어린이보호구역 위험란 일부구역에 대해 등하교 시간등 일부시간 화물승하차를 금지함으로써
+교통사고 미연에 방지
+다
+.
+급변하는 교통환경에 적극적 행정으로 안전사고 사전예방</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5245,10 +6339,8 @@
           <t>2023-09-26</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="E58" t="n">
+        <v>2023</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -5307,6 +6399,30 @@
         </is>
       </c>
       <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>아이와 시민들의 건강과 올바른 흡연습관을 위해 제안합니다.
+출, 퇴근이 길이나 주말 경우 담배를 피면서 보행하는 흡연자들을 쉽게 볼 수 있습니다.
+걸어가면서 담배를 피면 뒤에서 걷고 있는 노약자, 임산부, 환자, 어린아이, 학생 등 많은 사람들이 이러한 행위해 자신도 모르게 암에 걸리고 있습니다.
+간접흡연은 굉장히 위험하며 몸이 약하거나 불편한 사람은 폐암에 걸릴 확률 또한 높습니다.
+국내
+사망률 1위
+인
+폐암
+은
+생존률이 28%
+에 해당하고 있습니다.
+간접흡연은 직접흡연보다 폐암에 걸릴 확률이 1.5배가 높습니다.
+흡연자들의 시민의식이 개선되지 않기 때문에 다른 방법들이 필요한 것 같습니다.
+담배꽁초 버리는 건 현재 경범죄로 추가되어 있는데 여기에 더해
+보행 중 흡연 또한 경범죄로 추가하여 시민의 건강을 나라가 지켜줘야 할 것 같아 제안하게 됩니다.</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5329,10 +6445,8 @@
           <t>2023-08-10</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="E59" t="n">
+        <v>2023</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -5391,6 +6505,18 @@
         </is>
       </c>
       <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>안녕하세요? 용산 가족 공원을 자주 산책하는 주민입니다.
+요즘 건강을 위해 맨발걷기를 하는 사람들이 많아지고 있음을 봅니다. 저도 최근에 맨발 걷기를 시작했습니다. 다행이도 이곳에 걷기 적합한 흙으로된 트랙이 있음에 감사드리고 있습니다.
+다만 왕모로가 좀더  두껍게 깔려 있으면 맨발로 걷기에 더 좋을 것 같다는 생각을 하곤 합니다. 추가로 더 왕모래를 깔아주시면 좋겠습니다.</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5413,10 +6539,8 @@
           <t>2023-07-24</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="E60" t="n">
+        <v>2023</v>
       </c>
       <c r="F60" t="n">
         <v>25</v>
@@ -5475,6 +6599,32 @@
         </is>
       </c>
       <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>안녕하세요. 저희는 LG전자 ESG 대학생 아카데미 9기로 활동하고 있는 2조 '이심전심' 팀입니다.
+저희는 LG전자를 통해 ESG 실무자 교육 및 멘토링을 받고 있으며, 직접 ESG 활동을 기획하고 실행하고 있습니다.
+특히 7월 미션에서는 '다양한 사회/환경 이슈를 찾아보고 이를 해결할 수 있는 제품 및 기술 아이디어 제시'를 주제로 프로젝트를 진행하고 있습니다. 이에 노인 버스 승하차 시 넘어짐 사고 관련한 해결방안을 모색하였습니다.
+결론적으로, 저희는 이동약자인 노인에 대한 사회적 배려 의식을 고취시키기 위해
+버스 내 배려 안내 멘트 도입과 하차 알리미 시스템 설치
+를 제안하고자 합니다.
+먼저
+버스 승차 시
+, 카드를 태그하자마자 급 출발을 한다면 몸의 중심을 잃거나 넘어지는 위험에 노출되기 쉽습니다. 이러한 사고를 예방하기 위해
+어르신들이 시니어패스(수도권 내 만 65세 이상 노인이라면 발급이 가능한 교통카드)를 태그하면 특정 배려 안내 멘트가 송출
+되도록 합니다. 멘트 내용은 다음과 같습니다. "잠깐! 할머니, 할아버지가 앉으실 때까지 기다려주세요". 목적은 버스 기사분들께서 노인분들이 자리에 착석하실 때까지 음성이 길게 송출됨으로써 조금 더 기다리도록 유도하고자 합니다.
+다음으로
+버스 하차 시
+, 버스 급정거로 인해 정차 전 미리 서 있으시다가 균형을 잃는 경우도 많습니다. 이러한 사고를 예방하기 위해 노약자석 근처 빨간 불의 하차벨 밑에
+초록 불의 하차 알리미를 설치할 것을 제안
+합니다. 목적은 승객에게 완전히 정차한 후 일어서야 한다는 신호를 주고, 하차하는데 걸리는 시간을 충분히 기다려준다는 인식을 심어주기 위함입니다. 원리를 설명드리자면, 빨간 불의 하차벨을 누른 후 버스가 완전히 정차하면, 운전사가 누르는 문 열림 버튼 옆 초록 불 송출 버튼이 눌립니다. 초록불 송신 버튼은 문 열림 버튼만 눌러도 송신버튼이 눌리도록 합니다. 버스 정차 후 뒷문이 열리는 타이밍에 초록 불이 켜지면서, 그 때 일어나서 하차해도 된다는 신호를 전달하고자 합니다.
+자세한 내용은 첨부파일에 있으며, 긴 글 읽어주셔서 감사합니다.</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5497,10 +6647,8 @@
           <t>2023-06-19</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="E61" t="n">
+        <v>2023</v>
       </c>
       <c r="F61" t="n">
         <v>1</v>
@@ -5559,6 +6707,20 @@
         </is>
       </c>
       <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>안녕하세요. 직장생활 하고있는 만27세 여성입니다. 요즘들어 가장 큰 고민은 결혼과 출산인데요. 현재 남자친구가 있으나 저와 비슷한 또래로 직장에 취업한지 이제 갓 일년 즈음 되었습니다.
+결혼과 임신/ 출산/육아에 대해서 얘기나누며 미래를 그려보는 요즘 집장만부터 시작해서 최소한 한명정도 애를 낳으려면 드는 비용을 마련하기 위해서는 둘다 맞벌이를 하며 최소 4~5년 정도는 일을 해야한다고 결론이 나왔습니다. 그렇게 된다면 신체 나이가 들고 노산의 확률이 높아지므로 장애아 출산을 걱정하게 되어 미래가 점점 불안하게 느껴집니다.
+그에 대비하기 위해서 올해 후반에서 내년 초에 난자냉동을 고려중인데 350~500 정도의 비용이 든다고 합니다. 젊고 건강한 난자로 건강한 아이를 출산하고 싶은 마음이 있는데, 비용이 중소기업 재직자가 감당하기엔 높은 금액이라 불안합니다.
+정책을 확인해보니 만 30세 부터 지원을 하던데 지원 연령을 조금 더 낮추어 20대의 난자로 건강한 아이를 출산할 수 있도록 대비하고 싶은 결혼적령기의 20대 후반 여성들을 뒷바쳐주었으면 좋겠습니다.
+오늘도 고생이 많으십니다. 감사합니다.</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5581,10 +6743,8 @@
           <t>2023-06-10</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="E62" t="n">
+        <v>2023</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -5643,6 +6803,28 @@
         </is>
       </c>
       <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>수유시설 관리 표준 가이드라인을 보면
+○ 수유시설이란 아기에게 수유(착유)가 필요할 때 언제든지 방문하여 편하게 이용할 수
+있는 안전하고 쾌적한 공간을 구성하고 있는 시설을 의미하며 시설 이용자에 따라
+다음과 같이 구분하여 정의한다.
+- 모유수유/착유실 : 엄마와 아기 또는 수유부 전용 공간으로 편안한 상태에서 모유수유에
+집중할 수 있고, 직접 모유수유가 어려운 경우 모유를 짜서 보관할 수 있도록 마련된 공간
+- 가족수유실 : 기존의 수유실 이용 대상(엄마와 아기)을 가족(아빠 포함)으로 확대한 개념
+으로 수유 외에도 기저귀 교환, 이유식 등 다양한 육아 활동이 가능한 공간
+입니다. 그러나 서울시내의 모유수유시설을 돌아다니다보면 '아기쉼터', '유아 휴게실', '수유실', '가족 수유실', '아기사랑방' 등으로 명칭이 다양하며
+영문조차도 ' Nursing room', 'Family Feeding Room', 'Mom's Lounge', 'Baby Lounge', Baby Care' 등등 각 설치 기관이나 관공서 담당자 또는 발주기관의 관심과 어휘 이해도에 따라 상이한 것이 현실입니다.
+모유수유시설의 한글 명칭과 영문 명칭의 통일이 필요합니다. 어렵지도 않은 일인데, 정부기관에서 통일을 하지 않으니 의무적으로 설치해야 하는 관공서나 공공기관 또는 각 시설에서는 한글 명칭으로  '아기쉼터', '유아 휴게실', '수유실', '가족 수유실', '아기사랑방' 등등 다양한 명칭을 사용하고 있고, 이에 따라 영문 명칭조차도 ' Nursing room', 'Family Feeding Room', 'Mom's Lounge', 'Baby Lounge', Baby Care' 등으로 다양한 것이 현실입니다.
+이런 점에 대해 정부기관에서 통일하기 곤란하면 서울시라도 나서서 서울시 관내의 모유수유시설에 대해 제안 플랫폼을 통해 서울시민들의 제안을 받고 전문가들의 의견을 수렴한 후 서울시민들이 투표할 수 있는  엠보팅과 같은 플랫폼을 이용하여 서울시민들이 가장 선호하는 모유수유시설의 한글 명칭과 영문 명칭을 통일하는 것입니다.
+모유수유시설의 한글 명칭과 영문 명칭의 통일은 예산 낭비를 막고, 모유수유시설에 대한 하나된 인식을 서울시민들이 인지하고 공유할 수 있게 하며, 상대방에게 설명하거나 사고발생시 장소를 언급함에 있어 의사소통의 문제가 발생하지 않도록 하는데 기여할 것입니다.</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5665,10 +6847,8 @@
           <t>2023-04-26</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="E63" t="n">
+        <v>2023</v>
       </c>
       <c r="F63" t="n">
         <v>5</v>
@@ -5727,6 +6907,20 @@
         </is>
       </c>
       <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>우리 아이들에게 예측할 수 없는
+사고의 위험에 대비하여
+실질적인
+혜택을 체감할 수 있도록 운영효율
+제고방안을 마련해 보았습니다</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5749,10 +6943,8 @@
           <t>2023-04-24</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="E64" t="n">
+        <v>2023</v>
       </c>
       <c r="F64" t="n">
         <v>1</v>
@@ -5811,6 +7003,33 @@
         </is>
       </c>
       <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>안녕하세요,
+대낫에 인도로 걷던 초등학생들이 음주운전 차량에 치여 사망하고, 평생 장애를 갖고 살아가야 하는 사고가 발생했습니다.
+서울특별시는 자체 법안을 만들어 아이들이, 시민들이 안전하고 건강하게 살 수 있는 특별시가 되도록 해주십시오.
+1. 음주운전 처벌 강화
+음주운전 발생시 특별히 처벌을 강화 하여 주시기 바랍니다.
+음주 단속 보단, 처벌이 더 강화 되길 서울시가 앞장서서 가중처벌 하여 주시기 바랍니다.
+다른 시와 차별화된 안전한 서울이 되게 해주세요.
+2. 길거리 흡연
+마스크 착용이 해제되면서 길거리에서 담배 피는 사람이 너무 많습니다.
+최근엔 바람도 많이 불어 멀리 서 까지 담배냄새가 날아 옵니다.
+이제 아이들은 거리에서 매연뿐만 아니라, 담배연기까지 맡아야 합니다.
+학교, 정류장, 지하철 등 금연 구역 지정은 효과가 미비합니다.
+흡연 부스를 많이 설치해 주십시오.
+흡연 부스를 경찰서 옆, 주민센터 옆 마다 추가 설치하여 주십시오.
+흡연부스의 담배연기는 밖으로 나오지 않게 제발 만들어주십시오.
+흡연부스 안에 자체 공기 정화기를 설치하고 거기에 발생하는 비용은 흡연자들이 부담하게 해주십시오.
+흡연부스 이외 흡연시 벌금이 아닌 강력 처벌 하여 주세요.
+서울시 랜드마크 건설도 좋지만, 앞으로 자라날 아이들이 건강하고 안전하게 자라 서울시의 (몸과 마음이) 건강한 사회 구성원으로 자라날 수 있도록 서울시가 앞장 서 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5833,10 +7052,8 @@
           <t>2023-03-27</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="E65" t="n">
+        <v>2023</v>
       </c>
       <c r="F65" t="n">
         <v>68</v>
@@ -5895,6 +7112,50 @@
         </is>
       </c>
       <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>□ 목적 : 스쿨존에서 초등학생보행중 휴대폰 사용으로 인한 사고 방지
+           어린이보호구역 사고 막는다‥보행 중 스마트폰 제한 (2022.07.20/뉴스투데이/MBC) ？
+           https://youtu.be/hOW3QOM0caU
+□ 우리아이들의 스쿨존은 지금,충/분/히 안전한가요?
+ - 횡단보도용 바닥신호등,스마트 횡단보도,횡단보도 음성안내 보조장치등
+   '횡단보도 신호등 연동 전용 장치'들이 등하굣길에서
+    아이들을 스몸비로 인한 위험으로부터 충분히 지켜줄 수 있을까요?
+ - ‘스몸비’사고 막자...세금 쏟아붓는데 효과는?
+   사고방지 장치들이 속속 도입되고 있지만 확실한 안전보장은어려운 상황,
+   길을 걸을때 폰을 보지 않는 것만이 위험을 차단하는유일한 방법(MBC, 2019.7)
+ - 상대적으로 훨씬 더 위험할 수 있는
+    ▲차와 사람이 뒤엉켜 다니는이면도로 ▲신호등 없는 횡단보도가
+    스몸비-키즈*에 대한 안전사각지대는 아닐까요?
+    *스몸비-키즈:스마트폰만 쳐다보고 걸어가는'스몸비(Smombie)족’과 '키즈(kids)'의 합성어로,
+    등하굣길에 스마트폰만 보고 다니는초등학생들을 가리키는 신조어
+□ ‘스쿨존은 어린이 사고존'이라 불릴 만큼 사고가 지속 발생
+   - 12세 이하 어린이 스쿨존사고 최근5년간 연간평균523건 발생
+      2017년比44건(9.2%),사상자70명(14.1%)증가(도로교통공단2021)
+   - 어린이 교통사고 사망10건 중1건은 스쿨존에서 발생(뉴시스)
+   - 스마트폰 보며 걷다가 차도로 불쑥…교통안전 블랙홀‘스몸비와의전쟁’
+      초등학생10명 중8명 걸으면서 휴대폰 사용(동아일보,삼성교통안전문화연구소)
+□ 수혜자 : 학생 및 보호자
+□ 대   상 : 7개 초등학교 스쿨존
+   2021년‘스쿨존내 어린이 사고 다발지’ 서울특별시 관내 7개소
+  강북구/강서구/관악구/노원구/은평구 각 1개소, 영등포구 2개소
+  수유초(강북구), 공진초(강서구), 난우초(관악구), 청계초(노원구),
+  도림초/선유초(영등포구). 갈현초(은평구)
+   (출처:도로교통공단 교통사고분석시스템TASS)
+   (분석조건:반경300m내,대상사고2건이상 또는 사망사고 발생지역)
+   **스쿨존:초등학교 및 유치원 주출입문에서 반경300m이내의주통학로를
+     보호구역으로 지정하여 교통안전시설물 및 도로부속물설치로
+     학생들의 안전한 통학공간을 확보하여 교통사고를 예방하기위한 제도
+□ 파급효과
+   서울특별시 전역 ‘스쿨존 사고다발지역 초등학교’중심으로 우선 확산하여
+   안전한 등하굣길 조성을 위한‘스쿨존 안전망’구축</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5917,10 +7178,8 @@
           <t>2023-03-10</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="E66" t="n">
+        <v>2023</v>
       </c>
       <c r="F66" t="n">
         <v>7</v>
@@ -5979,6 +7238,21 @@
         </is>
       </c>
       <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>자격증 공부를 위한 '교재비 지원' 정책을 제안합니다. 
+취업준비를 위해 자격증 공부를 시작하고자 해도 교재 비용에 대한 부담이 적지 않다고 생각합니다.
+따라서,
+- 온라인 서점에서 자격증 관련 서적은 요구조건에 맞는 대상자임을 인증하면 할인해주는 쿠폰을 발급하거나
+- 오프라인 서점에서만 사용할 수 있는 포인트 형식이나 문화상품권을 지급하는 등의 
+방식을 통해 교재비를 지원받는 정책을 제안드립니다.</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6001,10 +7275,8 @@
           <t>2022-12-12</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="E67" t="n">
+        <v>2022</v>
       </c>
       <c r="F67" t="n">
         <v>1</v>
@@ -6063,6 +7335,20 @@
         </is>
       </c>
       <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>요즘 소아응급 전문 의료진 부족으로 상급종합병원(3차)에서도 야간 소아응급환자를 받지 못한다고 합니다.
+제도적으로 재원을 마련해 구마다 적어도 한 병원은 소아응급환자를 받을 수 있도록 지원하는 것을 적극 건의드립니다.
+이천시는 예산지원을 통해 2023년부터 야간 소아응급진료를 시작한다고 합니다. (참고: http://www.joongboo.com/news/articleView.html?idxno=363569754)
+물론 서울도 현재 서울대어린이병원과 서울아산병원에서 소아응급환자를 받고 있지만, 인구수에 비해서 턱없이 부족합니다.
+영,소아들이 응급실 앞에서 발걸음을 돌리는 경우가 많으니, 숙고 부탁드립니다.</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6085,10 +7371,8 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="E68" t="n">
+        <v>2022</v>
       </c>
       <c r="F68" t="n">
         <v>2</v>
@@ -6147,6 +7431,18 @@
         </is>
       </c>
       <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>운전을 하다보면 자주 지나가는 도로가 아닌경우, 어린이 보호 구역인지 잘 모르거나 진입후 늦게 알게 될때가 종종 있는데,
+어린이 보호구역에선 운전자가 정면에서 보일수 있게 LED전광판 같은 불빛으로 눈에 띄게 알려주었으면 좋겠습니다!!
+특히 우회전시 횡단보고 근처에 우회전 신호등처럼 어린이보호 구역 알림표시를 불빛으로 하면 사고가 줄어들지 않을까 생갑됩니다.</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6169,10 +7465,8 @@
           <t>2022-11-18</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="E69" t="n">
+        <v>2022</v>
       </c>
       <c r="F69" t="n">
         <v>5</v>
@@ -6231,6 +7525,25 @@
         </is>
       </c>
       <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>서울형 키즈카페 너무 부럽습니다.
+은평구에도 어서 빨리 생겼으면 좋겠어요
+은평구에 아이들 정~~~말 많거든요? 그런데 이번 여름에 다른 지역으로 물놀이터 찾아 헤맬때
+정말 슬펐어요..(은평구는 제대로 된 물놀이터 없거든요). 은평구는 인구밀집은 엄청난데 아이들도 많고.. 그에비해 아이들 데리고 갈 곳이 없어요
+물론 양쪽부모 다 있고 여유있는 집들은 좋은데 놀러가고 이런 생각 안하겠지요
+근데 정말로 맞벌이 부부 랄지.. 한부모 가정이랄지.. 혼자서 육아를 하는 집들은 주말에 정말 어디 갈 데가 없어요
+가까운 키즈카페도 두 곳이나 문 닫고 그나마 있는 곳 찾아서 원정가야합니다. 아파트에 안 사는 사람들은
+놀이터도 찾아 헤매기 일쑤입니다. 서울시에서 부모가 행복한 서울~ 이렇게 표어를 내걸어도 괴리감이 느껴져요
+제가 느끼는 온도차가 심하달까요. 특정 구에만 설치하지마시고 대대적으로 같이 해주셨으면 좋겠고 구 내에서도
+경쟁이 치열하니 좀더 많이 개설해주셨으면 좋겠습니다.</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6253,10 +7566,8 @@
           <t>2022-10-30</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="E70" t="n">
+        <v>2022</v>
       </c>
       <c r="F70" t="n">
         <v>3</v>
@@ -6315,6 +7626,18 @@
         </is>
       </c>
       <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>인도에서 흡연하는 사람. 인도에서 주행하는 오토바이 너무 많습니다.
+유모차 끌고 다니기가 무섭게 많습니다.
+이런 기본적인 것도 해결못하는데 무슨 다른 복지를 말하고자합니까.</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6337,10 +7660,8 @@
           <t>2022-06-12</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="E71" t="n">
+        <v>2022</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -6399,6 +7720,16 @@
         </is>
       </c>
       <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>현재 대부분의 인강 사이트에서의 교재비는 2만원이 넘어갑니다. 서울런 정책에서 교재비 지원금으로 주는 2만원으로는 개념 교재 1권도 살 수 없습니다. 저소득층 교육 격차를 줄이기 위해 나온 정책임에도 강의만 무료로 제공될 뿐, 교재는 따로 구매해야한다는 점에서 교육 격차를 줄일 수 있는지 의문이 듭니다. 교재비 지원금을 늘려주세요.</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6421,10 +7752,8 @@
           <t>2022-02-22</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="E72" t="n">
+        <v>2022</v>
       </c>
       <c r="F72" t="n">
         <v>112</v>
@@ -6483,6 +7812,27 @@
         </is>
       </c>
       <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>존경하는 오세훈 서울시장 및 각 부처 관계자께 제안드립니다.
+저는 미취학 장애아동을 키우고 있는 부모입니다. 중증 뇌병변 장애인탓에 아직 스스로 앉거나 일어서지 못합니다. 하루에 대부분을 누워있고 식사시간에만 등받이 의자에 앉아있습니다.
+형편이 이렇다보니 머리를 자르기가 많이 힘이 듭니다. 유튜브를 찾아보며 혼자 독학하여 잘라주고있지만 독학으로 배운 헤어컷은 늘 삐뚤빼뚤 입니다. 큰 맘 먹고 동네 헤어샵을 데려가더라도 거절 당하거나 불편한 시선들로 마음만 상하고 돌아옵니다.
+저는 부모니깐 참을 수 있지만 소중한 내 자녀가 장애가 있다는 이유로 불편한 시선을 받는것은 참으로 부모로서 억장이 무너집니다.
+이에 간곡히 제안드립니다.
+다른 아이들 보다 몸이 불편한 우리 아이들이 편하게 이발을 할 수 있는 그런 공간을 마련하여 주십시오. 장애아동도 멋있게 머리를 자를 수 있게 도와주십시오.
+내곡동에 위치한
+서울시립어린이병원에 설치된다면
+그곳에서 재활을 받는 장애아동들이
+편하게 이용할 수 있을거라 생각됩니다.
+그외에 서울시 관할 재활센터나 장애인복지센터에 설치되어 운영되기를 희망합니다.
+존경하는 오세훈 서울시장 이하 각부처 관계자께서는 심도있는 검토를 부탁드립니다.</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6505,10 +7855,8 @@
           <t>2021-12-05</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="E73" t="n">
+        <v>2021</v>
       </c>
       <c r="F73" t="n">
         <v>16</v>
@@ -6567,6 +7915,28 @@
         </is>
       </c>
       <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>제  안  서
+안녕하십니까? 저희는 동대문구 소재 경희대학교에서 ‘세계와 시민’ 강의를 수강하고 있는 학생들입니다. 현재 ‘아동인권 감수성’을 주제로 프로젝트를 진행 중이며, 구체적으로
+‘아동을 위한 지역 사회의 시설 개선’
+을 내용으로 실천적인 활동을 진행하고 있습니다. ‘아동을 위한 놀이 시설 및 녹지 확보’와 관련하여 제안 드리고자 합니다.
+Ⅰ. 문제 상황
+경희대학교 인근의 &lt;회기 힐스테이트&gt;는 직접 방문하여, 주변의 다른 아파트들은 인터넷 지도 서비스를 이용하여 답사한 결과, 다음과 같은 공통된 문제점을 확인할 수 있었습니다.
+1. 놀이터 및 녹지 면적의 협소함
+첨부한 [사진]에서 볼 수 있듯이 아파트의 규모와 세대 수에 비해 어린이를 위한 놀이 공간의 규모가 현저히 협소하다는 것을 알 수 있습니다. 더불어 놀이터의 위치가 섬 형태로 서로 분산되어 있고, 아파트 단지가 주변 도로와 연립주택 및 점포로 둘러싸여 있어서 실질적으로 아파트에 거주하는 아동이 이용할 수 있는 놀이 시설은 가장 가까운 놀이터 한두 곳에 불과하다는 것을 알 수 있습니다. 충분한 녹지 공간 및 야외 놀이공간 확보는 아동의 성장과 발달에 있어 매우 중요하므로 개선이 필요합니다.
+2. 식수대, 화장실 등 시설 부족
+식수대 및 화장실 등은 아동이 야외활동을 하기 위해 부가적으로 필요한 시설이지만, 조사한 아파트 대부분이 이러한 시설을 갖추고 있지 않았습니다. 특히 식수대는 여름철 아동의 야외활동 과정에서 필요적으로 갖추어야 할 시설이므로 개선이 필요합니다.
+Ⅱ. 제안 내용
+저희는 위와 같은 문제의 원인이 아파트 건설을 위한 사업시행자 및 건설사의 아동을 위한 시설 마련의 유인이 없다는 것에 있다고 보고, 다음과 같은 행정적 제재가 필요하다고 보았습니다. 즉, 토지형질변경 또는 건축허가 등 아파트 건설사업을 위해 필요한 행정청의 수익적 행정처분에 관련 부관을 붙이는 행정규제가 이루어져야 합니다. 형질변경 및 건축허가 과정에서 아동을 위한 일정면적 이상의 녹지 및 놀이 시설을 확보할 것과, 각종 편의 시설을 제공할 것을 ‘부담’ 또는 ‘조건’의 형식으로 부관에 붙여 건설 과정에서 상기한 시설이 확보될 수 있도록 행정처분 기준을 신설 또는 수정해주실 것을 제안합니다.
+서울의 신규 아파트는 대부분 재개발 사업으로 이루어지고 있다는 점, 아파트 사업시행자는 서울의 높은 인구 밀도로 인해 높은 용적률을 확보하기 위한 압력을 받고 있다는 점 등을 고려하였을 때, 위와 같은 행정적 규제가 아동을 위한 시설 마련이라는 목적을 달성하는데 효과적이고도 최소한의 침해를 가져오는 것이라는 분석 하에 위와 같이 제안 드립니다.</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6589,10 +7959,8 @@
           <t>2021-12-01</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="E74" t="n">
+        <v>2021</v>
       </c>
       <c r="F74" t="n">
         <v>11</v>
@@ -6651,6 +8019,84 @@
         </is>
       </c>
       <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>안녕하세요
+.
+저희는 서울여자대학교에서 바롬인성교육
+III
+을 수강하고 있는
+‘
+전동킥보드 안전하게 타조
+’
+입니다
+.
+저희는 한 학기동안 전동킥보드 안전 라이딩을 위한 다양한 활동을 수행하고 있습니다
+.
+올해
+5
+월
+13
+일 이후 개정된 도로 교통법이 시행되면서 전동킥보드 관련 문제들이 조금씩 해결되고 있습니다
+.
+하지만 저희가 조사해 본 결과 어린이 보호 구역과 관련된 전동킥보드 법안이 많이 부족하다는 점을 알게 되었습니다
+.
+스쿨존에서 규정 속도 등의 안전 의무를 위반하다 사고를 낸 운전자는 가중 처벌을 받게 하는 민식이법이 전동킥보드 이용자들에게도 똑같이 적용된다는 점을 제외하고는 사고를 철저히 예방할 수 있도록 하는 시스템이 전혀 마련되어 있지 않습니다
+.
+그래서 저희는 어린이 보호 구역에서 전동킥보드의 속도 제한을 의무화하는 것을 제안합니다
+.
+이때 단순히 이용자들의 속도 조절뿐만 아니라
+,
+공유전동킥보드 업체가 어린이 보호 구역에서는 전동킥보드의 속도가 자동 감속되도록 보행자들을 위한 안전 서비스를 구축해야한다고 생각합니다
+.
+한 공유전동킥보드 업체의 경우 어린이보호구역 사고를 예방하기 위하여 전동킥보드가 어린이 보호구역으로 진입하는 경우
+,
+시속
+10km
+이내로 자동 감속되도록 설정됩니다
+.
+고객이 킥보드를 타고 어린이 보호구역에 진입하는 경우 킥보드의
+GPS(
+지리정보시스템
+)
+가 진입을 확인하고
+,
+속도를 제한하는 방식입니다
+.
+세종시의 공유 전동킥보드는 최대 속도가 시속
+20km
+로 제한되며 어린이 보호구역으로 들어가면 자동으로 속도가 시속
+10
+㎞
+이내로 줄어듭니다
+.
+또한
+“
+여기는 어린이 보호구역입니다
+”
+라는 안내방송이 나옵니다
+.
+세종시 관계자는 어린이보호구역에서 사고를 예방하기 위해 전동킥보드 속도를 조절하는 기능을 갖췄다며 전동킥보드가
+GPS
+를 통해 어린이보호구역을 인식해 자동으로 속도를 줄인다고 했습니다
+.
+이처럼 어린이 보호구역에서 전동킥보드 속도가 제한되도록 할 뿐만 아니라 전동킥보드가 어린이보호구역에 진입하면 자동으로 시속
+10km
+이내로 줄어들도록 하는 등의 시스템을 구축할 수 있도록 법안이 마련되어야 합니다
+.
+앞으로 안전한 전동킥보드 문화를 위해
+,
+시민 안전을 위해 정부와 전동킥보드 업체는 더욱 노력하는 것이 필요합니다
+.
+감사합니다
+.</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6673,10 +8119,8 @@
           <t>2021-11-19</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="E75" t="n">
+        <v>2021</v>
       </c>
       <c r="F75" t="n">
         <v>5</v>
@@ -6735,6 +8179,18 @@
         </is>
       </c>
       <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>매주 2번 정도 손주 재활진료를 받으려고 시립병원을 방문하고 있는 할머니입니다.
+여기에 오는 대부분의 아동들은 지체가 부자연한 아동으로 보호자의 도움으로 휠체어나 유모차를 이용하는 아동들입니다.
+주차장간격이 일반 주차장과 같아 몸이 불편한 아동들을 태우고 내리는 문제 또한 어렵고 유모차나 휠체어를 내리는데 많은 어려움이 있으니 주차장간격을 완화하여 주시기를 부탁드립니다.</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6757,10 +8213,8 @@
           <t>2021-10-21</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="E76" t="n">
+        <v>2021</v>
       </c>
       <c r="F76" t="n">
         <v>5</v>
@@ -6819,6 +8273,20 @@
         </is>
       </c>
       <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>어린이 보호구역 내 주정차 전면금지법에 대해서 매우 공감합니다.
+하지만 저는 미국에서 10여년 넘게 생활하다 귀국해 보니 한국에서의 좋은점과 선진국과 비교해 볼 때 아직 미흡한 점들이 잘 발견되곤 합니다.
+이시행령에 대해서도 미흡한점을 발견했는데 드랍과픽업을 할 수 있는 죤을 만든다면 좋겠다는 생각이 듭니다.
+오늘 시행 첫날인데도 뉴스를 보니 필요성을 느끼는많은 분들이 있음도 보았습니다.
+꼭 시정될 수 있기를 기대해 봅니다</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6841,10 +8309,8 @@
           <t>2021-10-12</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="E77" t="n">
+        <v>2021</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -6903,6 +8369,27 @@
         </is>
       </c>
       <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>제안이유
+자동차와 퀵보드, 자동차와 자전거가 함께 다니는 도로는 성인들에게도 위험천만한 환경입니다.
+퀵보드나 자전거의 이용이 대중화된지는 한참 되었으나, 어린시절부터 교통규칙에 대한 지도와 실습은 이루어지고 있지 않은 것이 현실 속에 어린이 교통사고는 꾸준히 증가하고 있는 추세입니다.
+따라서 어린이 교통사고를 예방하기 위해 어린아이 때부터 철저한 예방교육이 이루어지는 것이 필요하다는 생각을 하게 되었습니다.
+어린 시절부터 교통안전교육을 받으면 습관이 되어, 성인이 되어서도 교통질서를 잘 지킬 수 있게 될 것이고, 사고에 대한 경각심도 늘 가지고 안전하게 생활하게 될 것입니다.
+따라서 유치원과 초등학교내에 교통안전 교육과 실습을 할 수 있는 공간과 시간을 제공하는 교통안전 법을 제안하고자 합니다.
+주요내용
+유치원과 초등학교에 다니는 학생들이 직접 체험할 수 있는 교통안전교육을 위한 전용 시설을 제공한다.
+아동이 자전거와 인라인이나 킥보드를 탈 때에, 안전교육을 일정시간 수료한 이후 합격한 아동에게만 '어린이교통안전면허증'을 발급해준다.
+유치원과 초등학교에 설치가 어려운 경우 지역사회에서 공동으로 사용가능한 교통안전교육시설장을 설치한다.
+한달에 최소 한 번 이상 규칙적이고 정기적인 교육을 받도록 제공한다.
+또한 아동이 자전거와 퀵보드를 탈 수 있는 전용도로를 만들어 일반 자동차와의 사고를 미연에 방지하려고 하는 노력을 서울시에서는 계속적으로 이어나가야 한다고 생각합니다.</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6925,10 +8412,8 @@
           <t>2021-09-30</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="E78" t="n">
+        <v>2021</v>
       </c>
       <c r="F78" t="n">
         <v>2</v>
@@ -6987,6 +8472,37 @@
         </is>
       </c>
       <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>&lt;
+제안 배경
+&gt;
+장기간 코로나로 인해 아동
+,
+청소년의 돌봄은 사각지대에 내몰리고 있습니다
+.
+돌봄을 개인의 문제가 아닌 지역사회가 함께 해결할 문제임을 인식하고 행동해야 할 때입니다
+.
+돌봄을 필요로 하는 이들이 무엇을 원하는지 당사자인 학생들은 무엇이 필요한지 우리의 귀와 눈을 열고 그들의 소리를 들어야 합니다
+.
+&lt;
+제안 내용
+&gt;
+안전하게 활동하고 돌볼 수 있는 지역 내 공간과 프로그램이 필요합니다
+.
+어떻게 효율적으로 안전하게 운영할 수 있을지 함께 의견을 모아야 하며 이를 위해 학부모
+,
+학생
+,
+지역 사회 단체와 지자체의 소통 창구인 온라인 공론장을 열어줄 것을 제안합니다
+.</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7009,10 +8525,8 @@
           <t>2021-08-24</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="E79" t="n">
+        <v>2021</v>
       </c>
       <c r="F79" t="n">
         <v>5</v>
@@ -7071,6 +8585,22 @@
         </is>
       </c>
       <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>독립문 공원 길 건너편에 있는 "독립운동가 가족을 생각하는 작은집" 에 사용된 벽돌을 교체 해야 합니다.
+그 취지는 매우 고맙고 환영 할 일이지만
+이 구조물이 언제 완성 되었는지는 모르겠으나 우리나라에도 용도에 적합한 벽돌이 흔한데 무슨 이유 인지는 모르나
+중국벽돌로 조적 되어 있고 이보다 더 한심한 일은 중국 폐건물에서 나온 재생 벽돌을 사용하여 조적 되어 있습니다.
+간혹 일반 건축물에서 멋스럽다는 이유로 폐벽돌을 사용 하기는 하나
+어찌 "독립운동가 가족을 생각하는 작은집"을 이런 폐벽돌을 사용 했는지
+조속히 철거후 국내에서 용도에 맞는 벽돌로 교체 해야 합니다.</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7093,10 +8623,8 @@
           <t>2021-07-19</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="E80" t="n">
+        <v>2021</v>
       </c>
       <c r="F80" t="n">
         <v>11</v>
@@ -7155,6 +8683,23 @@
         </is>
       </c>
       <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>제조업 분야 스타트업 지원에 비해 상대적으로 지원 규모가 작은 비제조/비영리 스타트업 청년 지원 방안과 관련해 제안합니다.
+제안 내용 1) 스타트업을 위한 장기 공간 제공
+초기 자본이 부족한 스타트업에서 중요한 것 중 하나가 고정적 지출비를 줄이는 것입니다. 그 중에서도 공간 임대료가 차지하는 비율이 매우 큽니다. 민간과 정부에서 지원하는 공간 임대 사업들이 많지만 대부분 단기(6개월 미만 등)입니다. 장기로 사무실을 제공할 경우는 제조업이나 AI와 같은 특정 분야 사업에 한해서만 공간 임대를 장기적으로 해주고 있습니다. 특히, AI 기업의 경우 무료/저렴한 공간 임대를 장기간 (5년) 제공받아 안정적으로 성장할 수 있는 기반이 마련되기도 합니다. 이러한 정책을 특정 분야에 한정하지 말고, 다양한 분야의 스타트업 (비제조/비영리)에게 문을 열어서, 청년들이 도전하고 지속할 수 있는 발판을 마련해주면 좋겠습니다. 특히, 시에서 지원하는 사업들이 단기 공간 임대 사업이 너무 많은데, 중장기 공간 지원책을 마련해주시면 도전하는 청년들에게 큰 도움이 될 것 같습니다.
+제안 내용 2)
+비영리/비제조 분야 스타트업 청년 종사자를 위한 전/월세 등 주거 지원
+청년들을 지원하는 여러 주거 정책들이 나오고 있지만, 이러한 정책들은 항상 여러 조건이 붙습니다. 중소기업에서 일하는 청년들을 위한 정책은 있지만, 아직 수익이 발생하지 않는 초창기 스타트업을 운영하거나, 창업 멤버로 일하는 청년들은 자격 조건이 안되어 받지 못하는 지원들이 많습니다. 청년들을 위한 지원책에서 근로 형태에 대한 자격 요건을 완화하거나, 창업을 하는 청년들이 자격 조건이 인정받을 수 있도록 개정하여, 초기 창업에 도전하는 청년들이 주거 지원 혜택에서 소외되지 않았으면 좋겠습니다.
+제안 내용 3) 스타트업 상품 유통/홍보 구축
+제조업 스타트업의 경우 정부나 민간에서 상품을 유통하고 판매하고 자금을 지원받을 수 있는 많은 통로가 있습니다. 하지만 미디어 스타트업, 비영리 스타트업 등 비제조업 분야 스타트업은 자신들의 “상품”을 전시하고 홍보하여 소비자(독자)를 만날 수 있는 수단이 매우 적습니다. 비제조업 분야의 스타트업을 위한 다양한 형태의 상품들이 소개되고 판매될 수 있는 크라우드 펀딩이나 판촉/홍보 방법을 마련해준다면, 다양한 분야의 스타트업들이 더 많은 고객들에게 다가갈 수 있을 것같습니다.</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7177,10 +8722,8 @@
           <t>2021-07-15</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="E81" t="n">
+        <v>2021</v>
       </c>
       <c r="F81" t="n">
         <v>12</v>
@@ -7239,6 +8782,22 @@
         </is>
       </c>
       <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>안녕하세요 저는 두아이를 둔 아이엄마입니다. 이곳은 성산동 성산 이편한세상 2차 앞이에요
+보시다시피 우리 아이들은 이길을 지나야 학교에 갈수 있는데요 양쪽으로 주차되어 있는 차량 멀리보이는 아파트 담벼락 아래로 불법 주차되어있는 차량으로 인해 이편한세상1.2차에 사는 아이들의 통학로가 매일 막혀있습니다
+차량때문에 더 아이들과 사람들이 걸을수가 없는 상태구요 매번 주차단속을 벌인다 하더라도 한계가 있습니다. 구청민원실에서는 길이 좁아 인도설치가 힘들다는 답변 받았구요. 하지만 차도 양방향 못지나가는 도로인데 굳이 양방향 통행을 할필요가 있을까요?
+1. 일방통행으로 한쪽에는 인도설치를 부탁드립니다.
+2. 아이들 걸을수 있게 50센치 폭이라도 울타리만이라도 설치좀 해주세요
+3. 이거저거 다 안되면 cctv하나 없는 골목길 입니다. 주정차 단속cctv달아서 절대 불법주차가 없도록 해주세요
+정말 부탁드립니다</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7261,10 +8820,8 @@
           <t>2021-07-15</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="E82" t="n">
+        <v>2021</v>
       </c>
       <c r="F82" t="n">
         <v>7</v>
@@ -7323,6 +8880,25 @@
         </is>
       </c>
       <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>안녕하세요
+메일로 필수목적 예방접종 신청을 하는데, 수시로 메일박스가 풀이 나서 리턴이 되고 있습니다.
+전화연결도 쉽지 않고, 신청하는게 너무 어렵습니다...
+빠른 해결을 부탁드립니다.
+1. This is an automatically generated
+Delivery Status Notification (Failure).
+2. The reason of the delivery failure
+was :
+452 Mailbox full
+zhfhskqortls19@seoul.go.kr</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7345,10 +8921,8 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="E83" t="n">
+        <v>2021</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -7407,6 +8981,21 @@
         </is>
       </c>
       <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>56년생 5월에 접종 예약했다가 검사에서 뇌경색병변이 나와 병원검사 일정으로
+예약을 취소했다가 이번에 다시 예약을 하려는데 하려는데 대상자가 아니라는 문구만 뜨고
+질병청도 군청도 그 어디도 통화도 안됩니다.
+예약했다가 질병 등의 문제로 다시 예약할 수 있는 조건임에도 안되는 이유와
+도대체 그 어디도 답변받을 곳이 통화가 안되는 사항을 어떻게 해야 합니까.
+저는 언니의 예약대리자입니다.</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7429,10 +9018,8 @@
           <t>2021-07-09</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="E84" t="n">
+        <v>2021</v>
       </c>
       <c r="F84" t="n">
         <v>112</v>
@@ -7491,6 +9078,20 @@
         </is>
       </c>
       <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>새문안로 2길은 매일 아침, 저녁 잘못된 신호 체계로 인해 지속적인 교통 정체와 불법 중앙차선 위반 및 과속으로 사고의 위험이 도사리고 있는 길입니다. 새문안로 2길에서 새문안대로로 좌회전 가능 구간이 현재 흥국빌딩과 콘코디언빌딩 밖에 없어 좌회전 차량이 몰리고 있고 또한 새문안로 2길에서 3길(경희궁자이 및 정부 청사로의 출입차량)로 직진 차량 또한 몰려 두 방면의 차량이 좁은 2차로 구간에 몰려 극심한 정체를 유발하고 있습니다.
+더구나 이 구간은 덕수초등학교 및 광화문LG 어린이집, 롯데카드 어린이집을 비롯한 유초등 보육 및 교육기관으로의 등하원 길임에도 불구하고 대부분의 차들이 정지선 위반 및 횡단보도 정차, 심지어 과속으로 중앙선 위반까지 빈번히 행해지는 위험천만한 길이 되고 있어 언제라고 사고의 위험이 도사리고 있습니다.
+따라서 현재의 교통 체계를 변경, 주변의 길들로 교통량 분산이 시급하다고 생각됩니다.
+새문안로 및 새문안로2,3길의 교통 신호 체계 변경 및 새문안로 2길의 차선 조정, 확장 등을 요청합니다.
+현재의 교통 상황을 첨부하여 드리오니 참조부탁합니다.</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7513,10 +9114,8 @@
           <t>2021-07-05</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="E85" t="n">
+        <v>2021</v>
       </c>
       <c r="F85" t="n">
         <v>13</v>
@@ -7575,6 +9174,33 @@
         </is>
       </c>
       <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>어린이 보호구역 4거리 교차로에
+우회전차로
+횡단보도에 작은 방지턱 설치는 어떤가요?
+횡단보도 사고중 우회전 사고가
+아주  많은걸로 알고있으며
+우회전시 아이들이 잘안보입니다.
+특히나 큰 사거리일 경우
+카메라가잇어도
+속도가 붙기에...
+제가 얘기하는 건
+방지턱은 모든사거리,
+횡단보도 전체가 아니라
+우회전차로가 구별되어있을정도로
+큰 사거리이며
+횡단보도 좌측에만 설치하는것입니다.
+(좌측에만 설치해야하는 이유는
+보행자(유모차, 행안부에서 정하는 약자들이 이용하는 보행차  포함)
+는 우측통행시 방지턱이 방해될수있기 때문입니다.</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7597,10 +9223,8 @@
           <t>2021-06-04</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="E86" t="n">
+        <v>2021</v>
       </c>
       <c r="F86" t="n">
         <v>15</v>
@@ -7659,6 +9283,24 @@
         </is>
       </c>
       <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>안녕하세요.
+서울시 중구 소재의 회사로 출퇴근을 하며, 중구 소재의 직장 어린이집에 어린 자녀 2명을 보내는 엄마입니다.
+다름아니라 사무실 밀집 지역을 보면 (예를 들면 제가 있는 을지로입구역 인근) 직장 어린이집이 꽤 있는 것으로 보여지고 (네이* 지도를 통해 사무실 밀집지역에서 어린이집을 검색하면 직장 어린이집이 꽤나 많이 나옵니다.) 이 어린이집에 재원 중인 아동들도 꽤 있는 것으로 추정이 됩니다. (예시를 제 소재지로 하였으나, 사무실 밀집지역이라면 어디라도 동일할 것 같습니다.)
+그런데 주변을 둘러봐도 이 아이들이 잠시나마 뛰어 놀 곳은 없어보입니다.
+상업시설이 밀집되어 있는 지역은 (다시말하면 땅값이 비싼 지역은..) 어느 회사도, 어느 기관도 아이들을 위한 공간을 내어주기가 쉽지 않아 보입니다.
+아이들이 신체 활동을 할 수 있도록 아이들이 이용할 수 있는 어린이 놀이터를 서울시에서 주도하여 지어서 활용할 수 있도록 하면 어떨까요?
+아이들의 활발한 신체 활동이 그 시기의 아이들에게는 꼭 필요하며, 대다수의 시간을 보내는 어린이집 근처에서 이런 활동들을 할 수 있도록 하면 조금 더 좋을 것 같습니다.
+뛰어놀 놀이터가 없어서 회사 주변의 도보를 손잡고 걸어가며 산책만 하는 아이들을 보고 있자면 괜시리 미안한 마음이 드네요..
+긍정적으로 검토 부탁 드리겠습니다.</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7681,10 +9323,8 @@
           <t>2021-05-30</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="E87" t="n">
+        <v>2021</v>
       </c>
       <c r="F87" t="n">
         <v>11</v>
@@ -7743,6 +9383,18 @@
         </is>
       </c>
       <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>코로나19 예방접종증명서를 현재 A4용지로 교부하고 있는데 이는 휴대가 매우 불편하고 증서 필요시 일일이 제시해야 되는 번거로움이 있어서 최소 주민증록증 사이즈로 교부해주었으면 좋았을 것입니다.
+대외적으로 쉽게 판별되고 예방접종 독려 효과도 노릴수 있도록 접종증명 뱃지를 만들어 의무적으로 부착하는 규정을 만들것을 제안합니다.
+뱃지모양 : 첨부파일 참조</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7765,10 +9417,8 @@
           <t>2021-05-21</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="E88" t="n">
+        <v>2021</v>
       </c>
       <c r="F88" t="n">
         <v>18</v>
@@ -7827,6 +9477,24 @@
         </is>
       </c>
       <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>작은도서관을 운영중입니다.
+공간적인, 경제적인 문제로 잡지(신문 등) 류의 배치에 어려움이 있습니다.
+서울도서관 , 서울교육도서관 또는 지자체의 공공도서관의
+전자잡지류(또는 신문, 전자책) 열람할 수 있는 ID를 개인이 아닌
+작은도서관 별로 고유아이디를 배정해서 직접 서울도서관 회원가입 절차를 진행하지 않아도
+작은도서관 방문만으로 해당 잡지들(또는 신문, 전자책)을 볼 수 있도록 허용해준다면
+정보 격차에도 해소가 일면 될 것이고 보다 가깝게 도서관을 이용할 수 있을거라 생각됩니다.
+또한 도서관 입장에서는 비용적인 부분이나 공간적인 문제로 비치하지 못했던 잡지류 (또는 신문, 책)등을
+제공하여 보다 지역사회 주민들에게 보다 나은 서비스를 제공할 수 있을것이라 생각됩니다.</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7849,10 +9517,8 @@
           <t>2021-05-17</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="E89" t="n">
+        <v>2021</v>
       </c>
       <c r="F89" t="n">
         <v>6</v>
@@ -7911,6 +9577,16 @@
         </is>
       </c>
       <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>유기견들에게 예방접종을 해주세요 유기견들은 예방접종을 못해 아프거나 심장 사상충에 걸려 죽을수도 있습니다 저는 동물들을 좋아해서 유기견들이 아픈걸보면 마음이 아파집니다 그리고 동물들은 우리와 같은 생명입니다 그래서 유기견들에게 예방 접종시켜주셔야합니다 그래야 유기견들이 안 아프고 불행하지도 않을것입니다</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7933,10 +9609,8 @@
           <t>2021-05-06</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="E90" t="n">
+        <v>2021</v>
       </c>
       <c r="F90" t="n">
         <v>5</v>
@@ -7995,6 +9669,28 @@
         </is>
       </c>
       <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>코로나 예방접종 관련 업무로 고생이 많으십니다.
+본인은 소아청소년과 의사로 하루동안의 예방접종 예진 업무에 투입된 뒤 정말 많은 생각과 고민 끝에 그만 두었습니다.
+물론 제가 일한 지역의 공무원의 고압적인 태도로 기분이 많이 상한 것도 있지만 무엇보다 절차 상의 문제가 있어 이에 대한
+보완 수정이 필요할 것 같다는 생각 때문이었습니다.
+다음은 제가 생각한 문젯점과 해결 받안입니다.
+1. 일단 예진 의사의 역할 - 지금같은 예진은 사실 필요가 없습니다.무엇보다 더 중요한 것 접종자들의 vital sign, 즉, 체온 뿐 아니라 혈압과 맥박 등을 체크해서 문제가 있으면 접종 연기를 권유 드려야합니다. 그리고 일반 직원들이 접종자에게 알러지, 부작용 전반에 대한 상담을 해서 문제가 되는 부분이 있을 때 예진 의사가 보는 시스템으로 가야합니다.
+무조건 의사를 보게 하는 건 아무 의미가 없습니다.
+2. 따라서 의사의 서명과 사인 또한 필요한 사항이 아닙니다. 이건 특별히 의사가 관찰해야 하고 상담해야 하는 접종자, 그리고 특별히 상담을 받고 싶은 분만 설정해서 예진하고 사인하면 되는 사항입니다. 이미 접종자들은 접종 자체에 대해 많은 걸 듣고 오시고 공무원의 말을 빌리자면 이미 맞겠다고 사인하고 온 분들이시니까요. 그러니 이건 이미 앞서 체크하면서 사인을 한번 더 받으시면 될 문제입니다. 어떤 분들은 오늘 상황이 안 좋아 미루자고 아무리 권유를 드려도 협박조로 맞겠다고 하기도 합니다. 황당하고 끔찍한데 여기에 사인을 해야만 하는 것 또한 제게 큰 스트레스 였으니까요.
+3. 어차피 15~30분 기다려야 하는 상황이라면 이 때 TV 스크린으로 접종 전후로 어떻게 관리해야 하는지 알려주는 동영상을 계속 반복적으로 보여 주는 것이 어르신들에게 알리는 가장 좋은 방법 입니다.
+4. 아무리 접종자 수를 늘리는 게 중요하다고 위에서 강요해도 하루 수용할 수 있는 한계가 있습니다. 1일 인원수 조절이 필요합니다. 의사 한명당 볼 수 있는 인원, 그래야 확실하게 상담할 수 있습니다.
+5. 서울시에서 접종 전후 주의사항, 이럴 땐 미뤄야 한다는 것, 어르신 들은 화이자 백신을 계속 줄 것이라는 확신 (미루면 아스트라제니카 맞아야 하니 무조건 오늘 맞겠다고 억지 주장 펼치시는 어르신들이 꽤 됩니다.) 이런 전반적인 것에 대한 홍보가 무엇보다 중요합니다. 포괄적이고 대충 그냥 일단 맞으러 오세요는 아닙니다.
+예방접종은 부작용이 가장 큰 문제이지만 무엇보다 맞았을 때 항체 형성이 잘 되어야 합니다. 그러려면 왠만하면 상태가 좋을 때 맞아야 합니다. 우린 지금 초유의 사태를 맞이하고 있지만, 그러나 무엇보다 이 백신의 효과와 장 단기적 부작용에 대해 알지 못하는 백신을 실험 중입니다. 그것도 인간한테요. (과장되게 들리실지 모르지만. 어쨌든 사실은 사실이니까요. 백신의 전반적인 걸 평가하기엔 너무 짧은 시간이니까요.) 그러니 제발 제 목소리에 귀 기울여 주시기를 간절히 바랍니다.
+여러분의 노고에 감사드립니다.</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -8017,10 +9713,8 @@
           <t>2021-03-30</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+      <c r="E91" t="n">
+        <v>2021</v>
       </c>
       <c r="F91" t="n">
         <v>22</v>
@@ -8079,6 +9773,34 @@
         </is>
       </c>
       <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>안녕하세요. 여러가지 제안을 지켜보던 중에, 지난 2018년도에 제안된 건을 보고 현재 실리적인 상황에 맞게  미혼여성으로 확대 도입해주시길 간곡히 요청드립니다.
+[현 상황]
+1) 30대후반 이후 여성의 결혼,출산율이 늘어나고 있음.
+2) 미혼 여성 중 만 35세 이상 여성 역시 증가
+3) 최근 여러사회이슈들 중 난임 시술이 증가함에 따라 알려져 관심이 증대
+4) 난임 지원사업이 점차 확대되고 있으나,실질적인 난임을 예방하는것은 사전 검진을 통한 확인 및 대비임.
+5) 실질적인 난임 시술은 난자 과배란을 통한 난자 추출을 바탕으로 진행되나 가장 중요한 것은 '난자의 질(Quality)'임. 난자는 의학적으로 하루라도 빠르게 냉동할수록 확률이 높아지며, 결혼이 예정에 없더라도 자신의 난자보유상태에 따라 현실적인 대비가 필요함.
+6) 결혼 이후 임신 준비를 시작하면 이미 때늦은 경우가 될 수 있음.
+7) 최근 난임전문의료진들이 진행하는 유튜브채널에서 보건소에서 AMH검사가 가능하다는 정보가 공유되어 정보를 알게되는 대상자가 많아짐
+https://youtu.be/SJLsfc3LgIc
+8) 서울시에서 2018년도 시범사업으로 진행되었던 난소나이검사는  일부 극히 적은 지역에서만 산전검사에 포함되어 진행, 또는 미진행되었음
+9)2021년 현재 지역구별 제각각시행되며, &lt;거주동민&gt;만 해당이 되어 타지역구민은 혜택이 불가함을 확인
+10) 본인이 거주하는 성북구는 산전검사를 받은 여성만 받을 수 있으며, 가까운 강북구의 경우 아예 검사를 시행하지 않고 있음.
+11)첨부파일 참고 시, 2018년 서울시 유관부서의 답변에 따르면 "35세 이상 여성을 대상으로 혼인 전
+？
+？검사를 통해  난소 나이를 측정 후  불임에 대한 예방적 대처를 통해 출산성공율을 높일수 있을 것이다" 라는 답변이 있으나, 실제 검사는 미혼 35세 이상의 여성은 혜택을 받지 못하고 '기혼'에게만 해당이 됨. 난자를 냉동하는 등의 예방적 대처는 '결혼'이 필수조건이 아님.
+&lt;결론&gt;
+현재 기혼 35세이상 여성에게만 한정하여 제공하는 난임관련 필요한 검사는 미혼여성들이 실질적으로 예방대처를 할 수 있도록 개정되어야한다고 봅니다.
+또한, 각 거주민이 해당 관할 보건소에서만 진행해야한다면 동일하게 시행하지 않는 곳 없도록 전체적으로 동일하게 집행해주세요.</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -8101,10 +9823,8 @@
           <t>2020-11-17</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="E92" t="n">
+        <v>2020</v>
       </c>
       <c r="F92" t="n">
         <v>31</v>
@@ -8163,6 +9883,16 @@
         </is>
       </c>
       <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>어린이보호구역내 횡단보도(신호등없는)에 노란 깃발을 설치해 주세요 아이들이 들고 있으면 차가 멈출수 있게요. 요즘 교통사고 나는거 보면 무섭습니다. 아이가 혼자 횡단보도 건너려 해도 차들이 멈춰주지 않아요  양쪽에서 오는 차들이 다 서거나 안 올때까지 하염없이 기다립니다 그러다 혹시 아이들이 급하게 가야 할 때면 어떻게 될까요? 서두르다 사고가 날수도 있죠 학교에서 모든 아이들에게 나눠주던지 아니면 신호등없는 횡단보도 마다 설치를 해주던지 했으면 좋겠어요</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -8185,10 +9915,8 @@
           <t>2020-11-03</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="E93" t="n">
+        <v>2020</v>
       </c>
       <c r="F93" t="n">
         <v>74</v>
@@ -8247,6 +9975,59 @@
         </is>
       </c>
       <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>퍼스널 모빌리티는 전통적으로
+레저와 여가취미
+생활에 이용되었고
+최근
+퍼스트-라스트마일 모빌리티
+로 관심을 받고 있습니다.
+더욱이 코로나19로 인한 언택트운동 확산에 따라
+대중교통의 안전 대체 수단
+으로 부상하고 있으며
+금년 도로교통법 개정으로
+이용기준이 완화
+되는 등 시장 성장에 더욱 탄력을 받고 있는 상황입니다.
+이런 성장과 함께 퍼스널모빌리티의 안전사고는 사회적인 문제가 되고 있으며
+다양한 퍼스널 모빌리티의 등장과 사용증가로 인해
+도심사고가 급증
+하고 있고
+사고율은 매년 2배 이상으로 급증하는 등 사회적 문제로 대두되고 있습니다.
+또한 도로교통법개정에 따른 이용기준완화로
+청소년의 안전에 심각한 우려
+가 예상됩니다.
+더욱이 서울시 자전거 하이웨이 구축 등의
+인프라 확충과 함께
+따릉이 자전거 자체의
+소통 장치 개선
+을 통한 이용자 안전을 위한
+새로운 아이디어가 적용되었으면 합니다.
+이에
+사고율이 높은 야간 시간의 사고 예방 소통장치를 적용
+하였으면 합니다.
+제품의 개발 컨셉은
+[시야 확보가 어려운 야간 시간에]
+- 퍼스널모빌리티의 구조적 한계를 극복하고 시인성 극대화를 통한 주시력을 향상시키고
+- 전,후,좌,우에서 운행 정보를 인지할 수 있어 다양한 충돌의 예방에 모두 대응이 가능하고
+- 다양한 정보를 통해 단방향(단순시그널)이 아닌 양방향 소통이 가능한 장치를 개발하게 되었습니다.
+해당 아이디어는 공기업 사내벤처로 지원을 받아 시제품개발을 완료하였으며
+서울시 따릉이와 함께 기술과 서비스를 고도화, 상품화
+하여
+서울시민은 물론
+국민의 안전에 기여
+하고 싶습니다.
+[제안내용서]
+첨부파일
+[아이디어 적용 홍보 영상]
+https://youtu.be/fOxXDibN9Oo</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -8269,10 +10050,8 @@
           <t>2020-10-25</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="E94" t="n">
+        <v>2020</v>
       </c>
       <c r="F94" t="n">
         <v>12</v>
@@ -8331,6 +10110,19 @@
         </is>
       </c>
       <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>근처 공원이라 북서울 꿈의숲에 아이들을 데리고 자주 산책을 갑니다 넓고 경치가 좋아 어른들 산책하기는 참 감사하고 좋으나 아이들 놀곳이 전망대 쪽 놀이터 뿐이라 항상 북적인다 생각하고 있었는데 최근 아래쪽에 유아숲체험장이 생긴것을 발견했습니다
+반가운 마음에 아이들과 가보았는데 기대와 달리 휑한 모습에 실망치 않을 수 없었습니다
+근래 일이 생겨 지방에 갔다가 지방 숲놀이터를 갔었는데 넘 비교가 되는 거 같아 제안합니다 아이들이 숲체험을 더 즐겁게 할 수 있도록 북서울 꿈의숲 공원  규모와 명성에 맞는 숲놀이터가 생겼으면 하는 바램입니다
+첨부사진은 정읍에 있는 아양사랑숲이라는 곳입니다 다양한 테마와 시설로 아이들이 즐거운 숲체험을 하고 있는 모습이 부러웠습니다</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -8353,10 +10145,8 @@
           <t>2020-08-25</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="E95" t="n">
+        <v>2020</v>
       </c>
       <c r="F95" t="n">
         <v>7</v>
@@ -8415,6 +10205,28 @@
         </is>
       </c>
       <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>안녕하세요.
+직장생활 중인 직장인 입니다.
+기업들이 모여있는 건물이나 기업사옥들을 보면 직원식당이 있습니다. 이러한 직원식당을 활용하여 끼니를 챙기기 힘든 아이들에게 식사를 제공할 수 있다면 얼마나 좋을까 해서 이러한 아이디어를 내봅니다.
+직원들이 이용하는 식당인 만큼 질좋고 영양가 있는 식단들이 골고루 나오는 장점이 있습니다.
+직원들이 붐비게 사용하는 점심식사시간이 아닌 조금 일찍은 시간이나 직장인들의 점심시간을 20분만 빗겨나가도 아이들이 충분히 영양가 있고 좋은 음식을 더욱 안전하고 쾌적한 곳에서 제공 받을 수 있다고 생각합니다.
+사실 직원식당을 이용해보면 생각보다 음식을 여유있게 만드셔서 항상 남아서 버려지는 것을 보게됩니다. 쓰레기를 매립할 장소도 부족한 요즘, 버리는 것이 아닌 필요한 곳에 나누는 것도 우리나라를 이끌어가는 기업들이 동참해야하는 것이라 생각합니다.
+또한 이러한 어린이 무료식사제공을 참여하는 기업에는 서울시에서 어떠한 혜택을 제공한다고 하면 기업이미지와 상생하는 모습을 마케팅으로 활용 할 수 있는덕에 참여하는 곳은 많아질 거라 생각합니다.
+또한 사춘기를 겪고있는 아이들이 가장 걱정하는 또래아이들의 눈치와 놀림거리보다는 현재의 엄마아빠 미래의 엄마아빠의 따뜻한 시선을 느낄 수 있는 장소라고 생각합니다.
+자녀를 키우고있는 부모 어느누가 "너 공짜밥 먹구나. 너 집이 형편이 안되구나" 라고 말하겠습니까.
+아이들이 편의점에 몇안되는 구석자리에서 매일같이 컵라면과 삼각김밥을 먹고 끼니를 때운다고 생각하면 마음이 아픕니다.
+매일 영양가 있게 짜여진 식단, 비가와도 눈이와도 쾌적한 공간에서 밥을 먹을 수 있는 권리를 찾아주는 것은 2020년을 살아가는 어른인 우리에게 주어진 숙제라 생각합니다.
+밥먹고살기가 힘들어는 옛말인줄 알았습니다. 자라나는 아이들에게는 해당안되는 말인줄 알았습니다.
+미래의 희망이 무궁무진한 아이들에게 따뜻한 밥을 제공해 줄 수있는 방안이 많이 생겨났으면 좋겠습니다.</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8437,10 +10249,8 @@
           <t>2020-08-24</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="E96" t="n">
+        <v>2020</v>
       </c>
       <c r="F96" t="n">
         <v>10</v>
@@ -8499,6 +10309,19 @@
         </is>
       </c>
       <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>비대면으로 인하여 택배물량이 많아지면서 아이스팩 사용량도 늘어나고 있습니다.
+집에 쌓여가는 아이스팩을 일반쓰레기로 버리기에 환경에 심각한 문제가 있지 않을까 싶습니다.
+각 주민센터마다 아이스팩 수거를 하여 개수를 정하여 휴지나 종량제봉투로 바꾸어주는 사업을 하면 좋을것 같습니다.
+아이스팩을 필요로 하는 사업자들에게는 나누어주어 아이스팩을 효율적을 사용했으면 합니다.</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8521,10 +10344,8 @@
           <t>2020-06-12</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="E97" t="n">
+        <v>2020</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
@@ -8583,6 +10404,21 @@
         </is>
       </c>
       <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>어린이보호구역내 교통사고가 계속 일어나고있습니다
+제 개인적인생각으로 어린이보호구역 내  도로를 반경300m 이내
+어린보호구역자체를 전부 과속방지턱으로 했으면 하는생각입니다
+우선 방지턱간격을 5m 내외로 해놓으면 차들이 제대로 달리지를 못하니
+과속우려가거의 없을꺼구요사고가나더라도경미한사고로 이어질수잇다고 생각합니다
+제 의견이 반영될지는모르겠지만 개인적인생각 적어봅니다.</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8605,10 +10441,8 @@
           <t>2020-05-24</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="E98" t="n">
+        <v>2020</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -8667,6 +10501,20 @@
         </is>
       </c>
       <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>어린이보호구역횡단보도 전면차단기설치 및인도난간무단횡단방지용으로재정비가 필요하다고생각됨.
+법으로 중하게하는것도중요하지만 먼저 물리적으로최대한 사고를예방하는것이 더중하다생각됨.
+횡단보도같은경우 보행자측 차람측4면에 차단기를설치하면 차량은 아무래도속도를낼수없고 보행자측도 무단횡단을어느정도방지할수있음.만약차량이 속도조절을못해 차단기파손이나 속도위반이되었을경우 기존에받았던처벌에서 기물파손에관한것도더해지며 .보행자가 무단횡단할경우 성인과어린이로 나뉘는데 성인은일반적으로받는처벌수위보다높게받아야한다고생각됨.어린이보호구역인만큼 아이들교육적인면에서 저해된다고봄.만약아이가 위반했을경우 보호자를 대동한교통안전교육을 의무적으로 몇시간이상을 들어야한다고봄.그를어길시 그또한 막중한처벌로 이루어져야함.그래야 이교통안전이라는것이 가정교육으로도 일루어질수있다고생각됨.
+그외 횡단보도외인도난간또한 절대로 넘어갈수없고 발헛디딤으로인한 사고방지를위한 무단횡단방지용난간으로꼼꼼한 재정비가필요하다고봄.어디로든지차도로 나갈수없겠끔.
+전 운전자인남편과 자식을둘 둔 엄마입니다.요즘민식이법이네뭐네하면서얘기가많더라구요.자식잃은부모나 안타깝게사고난운전자나모두내식구라생각하면 가슴아프겠더라구요.코로나로인해나라살림이말도아닐텐데도그리고 저만이런생각하는거아닐텐데도 꼭쓰고싶었습니다.효과가있을지는모르겠지만 모두가 조금이라도 안전해졌으면좋겠습니다</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8689,10 +10537,8 @@
           <t>2020-05-21</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="E99" t="n">
+        <v>2020</v>
       </c>
       <c r="F99" t="n">
         <v>1</v>
@@ -8751,6 +10597,24 @@
         </is>
       </c>
       <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>어린이 사고예방은
+운전자만 조심한다고 될 문제가 아니라고 봅니다.
+어린이 안전보행 교육강화
+부모교육 및 자녀의 안전보행의무 위반시 누적벌점제로
+일정기준의 벌점이 초과됐을 시 보육지원금 삭감과
+더이상 삭감할 지원금이 없을시 벌금을 부과하는 방법으로
+강력한 계도에 따른 어린이 안전보행 실현이 필요하다고 봅니다.
+또한. 어린이보호구역에서 등하교시간에 안전의무 불이행시
+가중처벌또한 이루어 져야한다고 봅니다.</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -8773,10 +10637,8 @@
           <t>2020-04-21</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="E100" t="n">
+        <v>2020</v>
       </c>
       <c r="F100" t="n">
         <v>6</v>
@@ -8835,6 +10697,24 @@
         </is>
       </c>
       <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>큰... 초등학교나 그옆의 도로
+뻘건색 아스팔트 정도는 .. 어린이 보호구역이라 알고있고 .. 대충봐도  어린이보호구역이란것이
+운전자한테 느껴집니다 ..
+근데 ... 왠 이상한골목이나 .. 한적한 도로가 .. 주변에 팬스 쳐진 공원에 빗물펌프장옆인데 ..
+이게 어린이 보호구역인지 뭔지 .. 알수가 없습니다 ... 도로고 검은색에 ...
+어린이 보호구역의 범위를 누구나 알아볼수있을만한 간판설치를 부탁드립니다 ...
+아니 법이 바껴서 이래저래 모자른것들은 .. 알겠는데 ..
+우린 이대로 그냥 할테니 모르면 모든 주정차.운행과태료 두배내라 .. ... 너무하는거아닙니까 ..
+애들은 보호하고 시민들은 봉으로 생각합니까 .....</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -8857,10 +10737,8 @@
           <t>2020-04-02</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="E101" t="n">
+        <v>2020</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
@@ -8919,6 +10797,17 @@
         </is>
       </c>
       <c r="R101" t="inlineStr"/>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>안녕하세요. 이번 코로나19로 코로나 아동수당 계획이 발표되었습니다. 사실상 코로나가 4월에도 계속되고..3-6월 분만하시는 분들은 산후조리원이나 도우미 쓰기도 꺼려지고 집에서만 보내야 하는 분들도 많습니다. 기사에서 해남시는 2020.4-6월 출생아에도 차등 지급을 한다고 명시가 되었는데, 서울은 발표 내용처럼 2020.3월생까지만 지급이 되는지 궁금합니다. 3-6월 지급해서 40만원 지급인데, 2020. 4월-6월 분만예정인 분들도 받았으면 좋겠습니다 :)
+다들 수고해주세요!</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8941,10 +10830,8 @@
           <t>2020-03-30</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="E102" t="n">
+        <v>2020</v>
       </c>
       <c r="F102" t="n">
         <v>5</v>
@@ -9003,6 +10890,24 @@
         </is>
       </c>
       <c r="R102" t="inlineStr"/>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>안녕하세요! 저는 유아교사를 직업으로 삼고 있는 서울 시민 강ㅇㅇ 이라고 합니다 :)
+이번 민식이 법이 생겨나면서, 어찌 보면 어린이들을 위해 당연히 생겼어야 할 법이기도 하지요! 하지만 제가 유아들을 교육하면서 느낀 유아들은, 절대 완벽한 통제를 할 수 없다는 것입니다.
+유아들은 신체적 욕구가 활발하고 에너지가 많아 뛰는 것을 좋아합니다.
+하고 싶은 일 (목표)가 생기면 그 목표만을 바라보고 달려갑니다.
+아이를 키우시는 부모님, 유치원, 보육교사 선생님들께서도 모두 공감하실거예요!
+그래서 저희가 차를 통제하는 것도 물론 좋지만, 언제 어디서 튀어나올지 모르는 어린이들을 물리적으로나마 막아줄 수 있는 장치를 설치했으면 좋겠습니다.
+제가 어떤 장치가 있을까 생각해 보다가 지하철 스크린도어가 생각이 났고, 어린이 보호구역에 한해서 횡단보도에 스크린도어를 설치한다면 조금 더 아이들과 운전자들이 안전한 서울시가 될 수 있지 않을까 생각을 해보았습니다!
+물론 도로와 인도가 정확하게 구분이 되지 않은 지역은 추가로 팬스를 설치하거나, 다른 대책들이 필요할 것입니다
+어린이들의 안전도, 우리 어른의 안전도 모두 생각할 수 있는 어린이보호구역 횡단보도 스크린도어 설치를 제안해봅니다!</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9025,10 +10930,8 @@
           <t>2020-03-26</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="E103" t="n">
+        <v>2020</v>
       </c>
       <c r="F103" t="n">
         <v>0</v>
@@ -9087,6 +10990,17 @@
         </is>
       </c>
       <c r="R103" t="inlineStr"/>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>민식이 법이 통과 된 후에도 차량들이 어린이 보호구역에서 속도를 줄이지 않고 지나 가고 있다는 뉴스보도를 보았습니다.
+법을 제정하는 것고 좋지만 실질적으로 현장에서 운전자들이 속도를 줄이지 않고는 지나갈 수 없는 환경을 만드는 게 훨씬 실효성이 크다고 봅니다. 그래서 어린이 보호구역에서 과속방지 턱을 높이거나 두개 이상 연속으로 설치해서 속도를 줄이지 않고는 지나갈 수 없게 하자는 제안을 드립니다.</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9109,10 +11023,8 @@
           <t>2020-03-16</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="E104" t="n">
+        <v>2020</v>
       </c>
       <c r="F104" t="n">
         <v>2</v>
@@ -9171,6 +11083,35 @@
         </is>
       </c>
       <c r="R104" t="inlineStr"/>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>현황 및 문제점
+1. 저출산의 문제점중 육아비용 부담이 있으며, 그중
+매일 사용 하는 기저귀, 폐기저귀 처리용 종량제
+봉투 구입 비용이 있음.
+2. 저소득층의  경우 종량제 구입비용도 육아 비용에      부담 될 수 있음
+3. 기저귀의 경우 재활용이 가능 함.
+4. 병의원,요양원에서 사용하는 기저귀의 경우
+분리배출 하여야 하나 비용의 부담으로 혼합배출
+하는 사례가 빈번히 발생됨.
+5. 기저귀를 재활용 하는 의견이나 폐기소각 하는
+의견이 있는데 이 모두 분리배출이 전제조건임.
+제안내용
+서울시에서 자체적으로 기저귀 전용 배출봉투를
+제작하여 가정용은 소형으로 무료 배포,
+병의원용은 중대형으로 저렴한 가격에 제공.
+기대효과
+가정용, 의료용 기저귀의 분리배출이 가능해져
+재활용, 폐기시 수훨하게 처리 가능.
+가정용배포로 육아비용이 절감 되고,
+의료용 혼합배출을 예방 할 수 있음.</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9193,10 +11134,8 @@
           <t>2020-03-11</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="E105" t="n">
+        <v>2020</v>
       </c>
       <c r="F105" t="n">
         <v>1</v>
@@ -9255,6 +11194,30 @@
         </is>
       </c>
       <c r="R105" t="inlineStr"/>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>아동수당 추가 지급 (추경이 통과되면 상품권으로 동사무소 등에서 지급한다고 뉴스에서 봤는데 이거 문제 아닌가요?
+전국적으로 확산되고 있는 코로나와 관련 현 정부시책 및 국민의 다수 의견은 최대한 사람간의 접촉을 피하는 것이 가장 급선무이며 중차대한 예방의 선결과제이다.(
+서울시도 사회적 거리두기 하고 있잖아요
+)
+헌데 아동양육 한시지원의 정책 중 10만원 상당의 지류(상품권 지급)은 다음과 같은 문제점을 야기시켜요.
+1. 반드시 대면 접촉을 하게 된다는 점 -동 등 에서 지류로 배부 할 시 아동 가족 그 누군가와는 반드시 대면 접촉을 하게 되는 점
+2. 등기 발송 시 또한 등기 수령인과 반드시 대면 접촉을 하게 된다는 점
+3. 지류로 받은 아동 가족 중 누군가는 반드시 지류를 쓰기 위하여 지역 시장, 마트 등을 방문해야 한다는 점
+4. 위와 같은 상황은 현 정부의 방역시책에 역행할 뿐만 아니라 잠재적 감염상태에 무방비 노출되어 현 사태에 전혀 도움이 되지 않는 점
+5. 지류로 배부 하였다 하여도 코로나 사태가 나아질 때 까지 대부분 외출을 삼가 하기 때문에 현 아동에 직접적인 도움이 되지 못한 다는 점
+6. 소비가 이루어지지 않기 때문에 아동 가구나 지역경제에 전혀 도움이 되지 못한다는 점
+정말 답답한 생각이 들어서 글 올리는데 적어도 서울시에서 만큼은 현금으로 지급 하면 안되나요?
+그게 가구에 훨씬 도움이 되고 온라인으로 구매 할 수 있고 사회적 거리두기 정책에도 맞는거 아닌가요?
+실시 여부가 아직 미확정이라고 하지만 뉴스를 보다가 참 어이없어서 적어도 우리 서울시 만큼은
+만약 한다면 현금으로 지급 했으면 하는 생각에 제안 해 봅니다.</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -9277,10 +11240,8 @@
           <t>2020-02-26</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="E106" t="n">
+        <v>2020</v>
       </c>
       <c r="F106" t="n">
         <v>4</v>
@@ -9339,6 +11300,23 @@
         </is>
       </c>
       <c r="R106" t="inlineStr"/>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>코로나19로 많은 자영업자들이 피해를 보고 있습니다.
+개학이 연기되고 학생들의 안전을 위하여 많은 학원들도 피해를 감수하고 교육부의 학원 휴원 권고 지침에 따라 코로나19가 더이상 확산되지 않기위해 휴원을 하고 있습니다.
+휴원중임에도 불구하고 나가는 월세, 강사월급과 더불어 3월 매출이 없음도 부담스럽지만,
+이 상황에서 휴원함으로 다시 되돌려 드려야하는 1주일에서 2주일치의 원비 반환이 현재 매출이 없는 상황에서 너무 힘이 듭니다.
+학원비를 현금으로 돌려드리는 대신, 학원에서 재사용하실 수 있는 지역상품권으로 돌려드린다면
+학원측에서는 당장 자금부족을 이겨낼 수 있고, 학부모측에서는 학원비로 재사용 하실 수 있으니 양해해주실 것 같습니다.
+학원도 자영업자인데, 아이들 건강을 위해 2주 휴원을 합니다. 방학 내내 비수기를 겪고 3월 신학기로 매출을 극복해야하는 시기에
+더 어려움을 겪는 학원 원장들에게 힘이 되어주시길 바랍니다.</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9361,10 +11339,8 @@
           <t>2019-12-07</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="E107" t="n">
+        <v>2019</v>
       </c>
       <c r="F107" t="n">
         <v>0</v>
@@ -9423,6 +11399,21 @@
         </is>
       </c>
       <c r="R107" t="inlineStr"/>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>일전에 식사를 하러 간 식당에서 옆 테이블에서 아이 기저귀를 가는 광경을 목격하고 식욕을 잃고 식사 도중 자리를 뜬 적이 있습니다. 당시에는 너무 불쾌한 경험이었고 그 손님들이 무례하고 비상식적인 사람들이라고 치부했지만 돌이켜 생각해보면 오래된 상가 건물에 위치한 동네 식당의 어디에도 수유실이 없을 거라는 사실은 명백했습니다. 그 부부가 식당 내부가 아닌 다른 어디에서 기저귀를 갈 수 있었을까요?
+영유아를 동반해 외출하는 경우 아이의 기저귀를 갈아줄 수유실은 절대적으로 필요한 공간입니다. 때문에 영유아를 데리고 외출할 수 있는 공간이 백화점이나 쇼핑몰처럼 그런 시설이 잘 갖추어진 장소로 한정되기도 하고, 불편함을 무릅쓰고 자가용 뒷자리에서 기저귀를 갈아주는 경우도 많습니다. 자차가 없거나 여건이 안되는 경우에는 타인에게 민폐(?)를 줄 수 있는 공간에서 다른 사람들의 눈총을 받아 가며
+어쩔 수 없이 기저귀를 갈아주게 되기도 할 것입니다.
+만약 따릉이 앱처럼 지도 기반으로 현위치에서 가장 가까운 수유실이 어디인지 확인할 수 있는 앱이 출시된다면 영유아를 돌보아야 하는 입장에 처한 수많은 사람들에게 큰 도움이 될 것이라 생각합니다. 가임지도 따위가 아니라 이런 어플리케이션이 바로 아이를 낳아 기를 만한 사회를 만들어나가는데 조금이라도 기여할 수 있지 않을까요?
+더 나아가 단독 주택 소유자가 담을 허물고 주차장을 만들 때, 베란다나 옥상 등에 태양광 발전 설비를 마련할 때, 친환경 하이브리드 자동차를 구입할 때 정부나 지자체에서 보조금을 지급하는 것처럼 건물주가 리노베이션을 통해 일정 요건을 갖춘 수유실을 마련할 경우 리노베이션 비용의 일부를 지원하는 등의 정책을 편다면 더 바람직할 것 같습니다.
+서울시 수유실 찾기 어플리케이션 개발 및 출시와 수유실 신설 시 비용 지원 등에 대한 정책 검토를 희망합니다.</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9445,10 +11436,8 @@
           <t>2019-12-06</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="E108" t="n">
+        <v>2019</v>
       </c>
       <c r="F108" t="n">
         <v>2</v>
@@ -9507,6 +11496,44 @@
         </is>
       </c>
       <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>어린이보호구역 혹은 노인보호 구역은 도로 포장 자체를 다른 형식의 도로로 바꿔보는 건
+어떨까 싶습니다.
+그 구역마다 과속단속 cctv를 설치를 한다고는 하나 일단 설치율이 저조하며
+법적 의무사항은 아니라고 들엇습니다.
+그리고 정작 운전자가 그걸 잊고 빠르게 달려버리면 그만입니다.
+벌금내고 뭐...벌점 있고....근데 사고가 난다면 이야기는 달라집니다.
+그래서 아에 물리적인 부분에서 차량의 속도를 줄이게 만들면 어떨까 싶은겁니다.
+도로자체를 바꿔버리는 거죠
+예를 들어 일정구간은 방지턱으로만 도로를 만드는 겁니다.
+지금 처럼 한두개가 아닌 아에...도로 자체를 방지턱으로 만들어버리는거죠...
+운전자들은 과속방지턱 앞에서는 본인과 본인 차량의 리스크를 줄이기 위해 자동적으로 속도를 급격히 줄이기 마련입니다. 거의 습관처럼...
+저 또한 운전자 이기에 과속방지턱 앞에서는 급 줄이게 됩니다.
+혹은 지름 30cm 정도되는 얕고 넓은 홈을 도로 군데군데 만들어 두는 겁니다.
+미관상 이쁠것 같지는 않지만 예쁘게 만들면 그만이고,
+가끔 도로를 달리다보면 파져있는 부분을 밟으면 차가 크게 덜컹 거립니다.그래서 그곳 또한 운전자는 피하게 되고 조심스럽게 지나갑니다.
+왜냐...내차는 소중하다고 생각하니깐....ㅉㅉㅉ
+그러니 빠르게 달리면 차가 흔들리니 운전자는 속도를 줄일 수밖에 없겠죠?
+그리고 큰 덤프트럭이나 물건을 많이 적재한 트럭은 그 도로가 불편하면 다른 길로 돌아가겠죠. 굳이 초등학생이 많은 길로 오게 할 필요가 없을 것 같습니다.
+즉슨 제가 제안하고 싶은 부분은 어린이보호 구역을 운전자의 양심에 맡기는 것보다
+물리적인 차원에서 보행자는 불편함 없고 운전자 또한 서행을 했을 시 차량에 큰 문제가
+없을 정도의 도로형태를 만들면 어떨까 싶은 겁니다.
+전문가가 아니라 딱히 더 좋은 생각은 나지 않지만 적어도 300m 구간 사이에 1m 간격으로
+연속된 과속방지턱이 설치가 되어 있다면
+운전자인 저로써도 빨리 달리고 싶은 생각은
+없지 않을 까 싶습니다.
+더 좋은 아이디어가 있음 댓글 달아주세요.
+민식이법 같은 생명안전법안 처럼 법적으로 오래거걸리고 어려운 부분은 그것대로 해결하고!
+우리는 우리식으로 쉽게 먼저 도와주고 더 안전하게 할 수있는 방법이 있다면 그것을 먼저 행하는 것도 좋을 것같습니다. 도로포장 새로 하는게 법안 통과보다는 쉬울거아닙니까!
+맨날 괜한 걸로 세금 낭비하시지 마시고!!</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9529,10 +11556,8 @@
           <t>2019-10-10</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="E109" t="n">
+        <v>2019</v>
       </c>
       <c r="F109" t="n">
         <v>8</v>
@@ -9591,6 +11616,20 @@
         </is>
       </c>
       <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>요즘 젊은 부모들의 새로운 랜드마크가 될 수 있도록
+SNS 감성을 자랑할 수 있는
+아름다운 허브공원, 핑크뮬공원, 아름다운 카페, 먹거리촌 등을 담고 아이들이 즐거워 할 수 있는 특화거리나  유명 디자이너나 설치미술가들의 작품들을 전시하는 공간을 운영하면 좋을 것 같습니다.
+젊은 엄마 아빠의 감성을 자극하는 테마 공원조성을 통해
+아이들이 어린이대공원에 대한 기억이 쭉 이어져 100주년을 맞이하는 어린이 대공원이 되기를 바랍니다.</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -9613,10 +11652,8 @@
           <t>2019-09-24</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="E110" t="n">
+        <v>2019</v>
       </c>
       <c r="F110" t="n">
         <v>6</v>
@@ -9675,6 +11712,23 @@
         </is>
       </c>
       <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>손자를 돌보는 조부모들이
+아이와 함께 이용할 수 있는 공간이 아파트 단지 내, 마을에 있으면 좋겠습니다.
+노인정은 아이들과 함께 갈 수 없는 공간이고
+도서관도 아이들과 함께가기 어려운 문화입니다.
+(도서관에서 아이들과 이야기 나누는 걸 허용하지 않는 문화..)
+이야기도 나누고 책도 읽고
+커뮤니티 활동도 할 수 있는
+세대 복합 문화 공간이 필요합니다.</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9697,10 +11751,8 @@
           <t>2019-09-24</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="E111" t="n">
+        <v>2019</v>
       </c>
       <c r="F111" t="n">
         <v>1</v>
@@ -9759,6 +11811,17 @@
         </is>
       </c>
       <c r="R111" t="inlineStr"/>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>새벽이나 한밤 긴급 돌보미 지원이 필요한 경우가 있습니다
+어린이집 등원 전이나, 한밤에 갑자기 일하는 부모가 돌보기 어려울 때 이웃 할아버지 할머니들이 돌봐줄 수 있는 방법이 있으면 좋겠습니다.</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9781,10 +11844,8 @@
           <t>2019-08-04</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="E112" t="n">
+        <v>2019</v>
       </c>
       <c r="F112" t="n">
         <v>1</v>
@@ -9843,6 +11904,17 @@
         </is>
       </c>
       <c r="R112" t="inlineStr"/>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>현행도로의 30으로제한이 되어있는데 그구간보다는 이구간에  들어가는 횡단보도정지선에서  횡단보도좌우  실선을 모두 이무적으로지그재그로  법적으로의무화 해 주？으면 합니다. 서행인데이구간횡단보도는 도로사정에따라 간격이들쑥날쑥해 큰것은크고 좁은곳은 좁아 너무위험합니다  자전거도로까지생겨서 더 문제가아닌가합니다  보호구역과 그안의 횡단보도앞 측구의 거리는 일반도로 측구너비만큼 거리유지의무와 지그재그로 보호를 해주셨으면합니다
+지워제서다시작성</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9865,10 +11937,8 @@
           <t>2019-07-31</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="E113" t="n">
+        <v>2019</v>
       </c>
       <c r="F113" t="n">
         <v>55</v>
@@ -9927,6 +11997,19 @@
         </is>
       </c>
       <c r="R113" t="inlineStr"/>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>안녕하십니까? 저는 서울시 동작구에 살고 있는 '노회림' 입니다.
+저는 요즘 아동들이 놀 수 있는 실내공간이 더욱 많아져야 한다고 생각하고, 필요하다고 생각합니다. 요즘에는 미세먼지가 심한 날도 있고, 폭우가 쏟아지는 날, 또 폭염이 기승을 부리는 날도 있기 때문에 밖에서는 놀지 못할 때가 대다수 입니다. 그리고 키즈카페는 저학년들이 놀 수 있는 '키즈카페' 라는 공간이 있지만 그곳에는 고학년들이 가지 못하고, 요즘에는 키즈카페에 가는 초등학교 저학년도 많이 볼 수 없습니다. 그래서 저는 아동들이 편히 놀 수 있는 실내 놀이공간이 필요하다고 생각합니다.
+만약에 실내 공간에 '놀이시설'이 생긴다면 어떤 놀이시설이 필요할까요? 먼저 활동적인 아동들을 위해 활동적인 아동들이 편히 이용할 수 있는 운동기구들이나 박진감 넘치는 모험 놀이터가 생기면 좋을 것이고, 예술적인 것을 좋아하는 아동들을 위해 자신의 생각을 자유롭게 표현할 수 있는 미술 공간이 필요할 것입니다.(+미술도구) 또한, 요즘 고학년들이 많이 찾는 만화방이나, 노래방도 필요할 것입니다. 또, 휴대폰 게임 말고, 카드게임이나 보드게임을 좋아하는 아동들도 있으므로 그런 시설을 들여놓는 것 또한 좋을 것입니다.
+요즘 아동들은 놀 권리에 대해 잘 모르고 있고, 공부하는 시간에 놀 시간을 뺏겨 잘 놀지 못하는 경우도 많습니다. (아동들의 공부시간이 성인들의 근무시간보다 많았습니다) 그럴수록 우리는 아동들의 놀 권리를 존중해주어야 하며 또한 아동들의 놀 권리의 필요성을 아는 것이 중요하다고 생각합니다. 감사합니다.</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9949,10 +12032,8 @@
           <t>2019-07-31</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="E114" t="n">
+        <v>2019</v>
       </c>
       <c r="F114" t="n">
         <v>8</v>
@@ -10011,6 +12092,17 @@
         </is>
       </c>
       <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>아이들만의 쉬는 공간이 필요해요! 부모님이 일하셔서 혼자있는 날이 많을 때. 어르신들의 무더위 쉼터처럼 저학년 고학년 학생들이 방학때만 편안히 놀 수 있는 곳이 생기면 좋겠다.
+(새솔초)</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -10033,10 +12125,8 @@
           <t>2019-07-31</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="E115" t="n">
+        <v>2019</v>
       </c>
       <c r="F115" t="n">
         <v>3</v>
@@ -10095,6 +12185,16 @@
         </is>
       </c>
       <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>저는 아이들을 위한 실내 시설이 더 필요하다고 생각합니다. 왜냐하면 실내 놀이 시설 같은 경우는 대부분 한정적이거나 나이 제한, 키 제한등이 있는 경우가 많은데, 유치원생이나 저학년만 사용할 수 있는 곳이 아닌 고학년들도 신나게 뛰어놀 수 있고, 책도 읽으며, 노래도 부르고 대화도 하면서 게임도 하고 음식도 먹을 수 있는 곳이 생긴다면 많은 고학년 들이 즐길 수 있고 핸드폰중독 연령대가 덜 낮아질 수 있지 않을까라고 생각합니다.</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -10117,10 +12217,8 @@
           <t>2019-04-26</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="E116" t="n">
+        <v>2019</v>
       </c>
       <c r="F116" t="n">
         <v>1</v>
@@ -10179,6 +12277,22 @@
         </is>
       </c>
       <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>키가 작은 어린이가 운전자의 시야에 잘 들어오도록 노란 고깔모자 착용
+*키가 작은 어린이가 운전자의 시야에 들어오지 않아 교통사고 발생이 잦음
+30cm 높이의 고깔모자를 제작하여, 어린이 등하원길 및 야외학습 시 착용토록 안내
+- 어린이집, 초등학교, 주민센터 등 고깔모자 만들기 활동 시행
+- 추진방법 : 구립어린이집을 1개소를 선정, 4세반 도는 5세반을 대상으로 시험시행후 확산
+* 예산등으로 추진이 어려울 경우 평생교육팀과 협력적으로 추진 가능
+어린이 교통사고 예방효과뿐만 아니라 학부모 등 보호자에게 심리적 안정을 줄 수 있다고 볼 수 있다</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -10201,10 +12315,8 @@
           <t>2019-03-08</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="E117" t="n">
+        <v>2019</v>
       </c>
       <c r="F117" t="n">
         <v>10</v>
@@ -10263,6 +12375,21 @@
         </is>
       </c>
       <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>길고양이의 개체수 증가로 인한 소음 및 사체처리 등 주민들의 민원이 빈발하고 있으므로
+길고양이들은 제대로 먹이를 찾지 못해 건강을 위협받고 여러 병균에 노출되어 위생상 문제도 발생하고 있어
+길고양이를 분양받고자 하는 이들도 분양후 양육비에 대한 부담으로 선뜻 분양받지 못하는 경우가 많음
+길고양이 중성화 수술을 통한 개체수 조절 및 효과적인 관리(길고양이 입양시 중성화 수술, 예방접종 비용 지원)
+길고양이 쉼터 조성(급식소 마련)을 통한 고양이 관련 민원 해소
+외로운 독거노인 등 반려동물을 원하는 사람들에게 분양 후 양육비 보조</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -10285,10 +12412,8 @@
           <t>2019-02-27</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="E118" t="n">
+        <v>2019</v>
       </c>
       <c r="F118" t="n">
         <v>2</v>
@@ -10347,6 +12472,17 @@
         </is>
       </c>
       <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>• 어르신을 고용하여 어린이 놀이터, 미니 공원에 설치된 모든 놀이기구 점검 및 시설을 이용하는
+아이들 돌봄하여 어르신 일자리 창출 및 아이들 안전사고에 대비하고자 함</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -10369,10 +12505,8 @@
           <t>2019-01-22</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="E119" t="n">
+        <v>2019</v>
       </c>
       <c r="F119" t="n">
         <v>0</v>
@@ -10431,6 +12565,18 @@
         </is>
       </c>
       <c r="R119" t="inlineStr"/>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>새소리, 웃음소리 지켜주세요
+이젠 더이상 편리두의 안됩니다
+자연의 역습 무섭잔아요  ㄲ오록 지켜주세요</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -10453,10 +12599,8 @@
           <t>2018-11-27</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+      <c r="E120" t="n">
+        <v>2018</v>
       </c>
       <c r="F120" t="n">
         <v>294</v>
@@ -10515,6 +12659,18 @@
         </is>
       </c>
       <c r="R120" t="inlineStr"/>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>현재 보건소에서 임산부를 위해서 임신반응검사부터 임신기초 검사를 받을 수 있고 임신확인 후 임산부를 위한 엽산이나 철분제(일정 주수 후)를 선물로 받을 수 있습니다.
+엽산은 임신을 준비하고 있는 분들은 챙겨 먹어야하는 영양제입니다. 임신 후에 엽산을 제공받는 것도 좋지만 임신을 준비하는 사람들을 위해서 미리 제공해주는 것은 어떨까요?
+예비맘키트라고 해서 배란테스트기와 임신테스트기 그리고 엽산이나 엽산이 들어간 종합영양제를 함께 준다면 좋을 것 같습니다. 추가적으로 임신과 출산에 관련된 국가정책(?)과 책자와 병원리스트(산부인과 및 난임병원)를 넣어서 준다면 임신을 준비하시는 분들에게 도움이 되리라 생각됩니다.</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -10537,10 +12693,8 @@
           <t>2018-10-24</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+      <c r="E121" t="n">
+        <v>2018</v>
       </c>
       <c r="F121" t="n">
         <v>0</v>
@@ -10599,6 +12753,21 @@
         </is>
       </c>
       <c r="R121" t="inlineStr"/>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>안녕하세요.
+다른곳도 마찬가지지만 특히 '어린이보호구역'의 불법주정차가 매우 심각합니다.
+물론 각자의 사정이 있고 이유가 있겠지만 사각지대 유발 및 아이들의 불편 그리고 교육상에도 불법 주정차는 좋을게 없습니다.
+그래서 어린이보호구역내의 불법주정차를 쉽게 신고할 수 있는 부서나 콜센터를 두고 관리를 했으면 합니다.
+막상 신고하려해도 번거로워 신고가 어려우니
+사진등을 첨부해서 신고하는 제도가 있었으면 합니다.</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10621,10 +12790,8 @@
           <t>2018-09-04</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+      <c r="E122" t="n">
+        <v>2018</v>
       </c>
       <c r="F122" t="n">
         <v>0</v>
@@ -10683,6 +12850,39 @@
         </is>
       </c>
       <c r="R122" t="inlineStr"/>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>아래 제안은 제가 지난달28일 햇던 내용입니다.
+점부할 사진이 있어 다시 올립니다.
+어린이 보호구역 신호등 노란색 칠하기
+이동석
+님
+2018-08-29 10:20
+어린이 보호구역 이나
+노인 보호구역이 정해져 있습니다.
+스쿨죤 또는 아스팔트 위에 또는
+표지판으로도 표식이 되어 있지만
+신호등 기둥 그리고 신호등커버 전체를
+어린이보호구역이나 노인 보호구역 횡단보도 신호 또는
+차량 신호등에도 노랑색으로 전체를 칠하여
+아스팔트 바닥 또는 표지판을 못보더라도
+신호등 커버 기둥색깔이 노란색으로
+칠해져 있으면 누가봐도 어린이나 노인보효
+구역임이 표시 날겁니다.
+이러한 노란색으로 칠해져 있는 신호등커버 기둥이
+있는곳 에는 모든 운전자.자전거 오도바이등등이
+서행하여 어린이나  노약자들을 보호 햇으면
+좋겟다？ 생각이 들어
+제안하여 봅니다.
+공감 1건
+공감</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -10705,10 +12905,8 @@
           <t>2018-08-29</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+      <c r="E123" t="n">
+        <v>2018</v>
       </c>
       <c r="F123" t="n">
         <v>1</v>
@@ -10767,6 +12965,31 @@
         </is>
       </c>
       <c r="R123" t="inlineStr"/>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>어린이 보호구역 이나
+노인 보호구역이 정해져 있습니다.
+스쿨죤 또는 아스팔트 위에 또는
+표지판으로도 표식이 되어 있지만
+신호등 기둥 그리고 신호등커버 전체를
+어린이보호구역이나 노인 보호구역 횡단보도 신호 또는
+차량 신호등에도 노랑색으로 전체를 칠하여
+아스팔트 바닥 또는 표지판을 못보더라도
+신호등 커버 기둥색깔이 노란색으로
+칠해져 있으면 누가봐도 어린이나 노인보효
+구역임이 표시 날겁니다.
+이러한 노란색으로 칠해져 있는 신호등커버 기둥이
+있는곳 에는 모든 운전자.자전거 오도바이등등이
+서행하여  노약자들을 보호 햇으면
+좋겟다？ 생각이 들어
+제안하여 봅니다</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10789,10 +13012,8 @@
           <t>2018-08-22</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+      <c r="E124" t="n">
+        <v>2018</v>
       </c>
       <c r="F124" t="n">
         <v>3</v>
@@ -10851,6 +13072,19 @@
         </is>
       </c>
       <c r="R124" t="inlineStr"/>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>안녕하세요.
+어린이 보호구역에 신호등이나 과속방지턱, 안내판 정도로는 실효과 크지 않은 것 같습니다.
+바닥을 울퉁불퉁한 돌벽돌로 만들어 놓으면 미관상에도 매우 좋고 차량 운전자들은 어쩔 수 없이 서행하게 되어 실효로 이어질 수 밖에 없을 것 같습니다.
+고려해 주시길 부탁드립니다.</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -10873,10 +13107,8 @@
           <t>2018-08-10</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+      <c r="E125" t="n">
+        <v>2018</v>
       </c>
       <c r="F125" t="n">
         <v>0</v>
@@ -10935,6 +13167,51 @@
         </is>
       </c>
       <c r="R125" t="inlineStr"/>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>30대 후반 맞벌이 부부입니다.
+5세, 7세 아이들이 있구요.. 지금은 같은 어린이집을 다니고 있어서
+제가 아침일찍 등원을 시키고 출근을 합니다.
+하원은 양가 부모님께서 요일별로 나눠서 도와주시구요.
+그래도 전 다행인 편에 속합니다.
+회사가 가까워서 등원을 시키는 일이 가능하고
+양가 부모님이 근처에 사셔서 하원을 도와주시는것도 가능합니다.
+그런데 걱정이 하나 있습니다.
+내년에는 큰애가 초등학교에 다니게 되어 여러가지 고민거리가 생겼습니다.
+1. 등원에 대한 동선. 어린이집과 초등학교 위치가 반대여서 등원을 어떻게 시켜야 할지가 고민입니다.
+2. 초등학교 하원 후 케어
+- 초등학교는 오후 1시면 끝납니다. 돌봄교실을 신청하거나 학원 뺑뺑이를 돌려야 하는데..
+학원 차량까지 연계는 누가 해줄지... 돌봄교실이 끝나고 하원은 누가 도와줄지...
+큰 문제는 이 두가지 입니다.
+즉, 등/하원의 어려움 입니다.
+이래서 초등학교 입학 즈음에는 맞벌이가 외벌이로 바뀔 수 밖에 없다 하더군요..
+저희같이 양가 부모님께서 도와주시거나
+형편이 되는 가정에서는 도우미를 쓰곤 하는데,
+도우미는 보통 180~200정도로 등/하원 뿐만 아니라 가사도우미까지 병행하고 있습니다.
+부모 입장에서는 등/하원시만 도와주면 좋은데.. 그렇게되면 시급으로 하루 3시간도 안될거거든요.
+그래서 제안드립니다.
+ㅇ 도우미 입장 : 근로자로서 일정 수익이 담보되어야 합니다.
+ㅇ 부모 입장 :  도우미 비용이 부담되고.. 가사지원 보다는 등/하원이 최 우선으로 필요합니다.
+그렇다면..
+등/하원시에는 도우미 이용에 대해서는 부모가 부담을 하고 (시급 1만원이면 일 3만원, 월 60만원 정도로 부담이 줄어듭니다)
+나머지 시간에는 도움이 필요한 곳에 도우미가 가는 거죠..
+도움이 필요한 곳이란? 어린이집 선생님, 장애인돌봄, 노인돌봄, 사회복지사와 같이 월 52시간 근무에서 제외되는
+업무들입니다.
+어린이집 선생님을 예로 들면..
+하루 8시간 풀로 일하고 밥먹을 때에도 아이들과 같이 밥을 먹으면서 한시도 쉴 수 없습니다.
+이런 분야에 도우미가 투입되서 2~3시간정도 지원을 해 주시면
+어린이집 선생님들도 쉬실 수 있게 되겠죠.
+또, 초등학교 저학년 어린이들을 케어하거나
+학교 - 학원버스 연계 도우미로도 활용이 가능할겁니다.
+비용은 해당 기관에서 일부 부담하고, 일부는 세금으로도 충당하면 좋을거 같습니다.
+☆ 등하원 돌보미를 활용한 일자리 창출. 어떤가요?</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -10957,10 +13234,8 @@
           <t>2018-05-20</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+      <c r="E126" t="n">
+        <v>2018</v>
       </c>
       <c r="F126" t="n">
         <v>0</v>
@@ -11019,6 +13294,32 @@
         </is>
       </c>
       <c r="R126" t="inlineStr"/>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>재건축, 재개발, 도시 재생, 도시공학, 리모델링 등등 화려한 수사를 보면서 여러 생각을 하게 된다.
+기본적으로 자기 이익을 추구하려는 시각에서 출발하고 있다고 본다.
+살다보면 청소년들이나 아동들이 놀이터에서 놀기위해서 모여 있거나 놀이터로 오가는 모습을 본다.
+군데군데 소규모 공터였거나 남는 땅을 녹지 약간 조성하고 그네같은 놀이기구 몇개 놔둔 아주 소박한 공간이다.
+그걸 보면
+컴퓨터 게임에 빠지지 않고 공원에 오는 것이 대견스럽기도하고
+서울이라는 도시 속에서 아이들이 공을 차거나 뛰어놀 공간이 없는 것은 30년 전이나 마찬가지 이구나 하는 감회가 생긴다.
+사회적 약자인 아동과 청소년은 별 관심은 못 받는 듯 하다.
+결론
+서울시 내에 녹지, 공원, 아동 청소년 및 노인까지 활용할 놀이터 등 사회적 자원을 확충해 주기 바란다.
+서울시가 하는 짓은 아니지만 빈 땅이 생기면 녹지나 휴식공간은 안 생기고 주차장만 생긴다.
+주차 수요에 대한 정책이 부재한 탓도 있지만
+차를 사용하는 자들이 바로 주도적인 계층이고 그들은 자기의 수요를 먼저 충족하기 때문이다.
+녹지의 경우 환경적 대안이고 심각하게 연구할 분야다.
+다만 꽃가루로 인한 보건적 문제는 사회적 비용을 증가시키고
+사람을 괴롭게 하는 요인이다.
+따라서 꽃가루 문제도 깊이 고려되어야 한다. 아무도 하지 않는 일같아 보이는데 그런 아무도 하지 않는 일을 해야 하는 것이 바로 정부, 지방정주, 아니면 서울시이다.</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -11041,10 +13342,8 @@
           <t>2018-05-14</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+      <c r="E127" t="n">
+        <v>2018</v>
       </c>
       <c r="F127" t="n">
         <v>6</v>
@@ -11103,6 +13402,36 @@
         </is>
       </c>
       <c r="R127" t="inlineStr"/>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>제목 : 월컴 키즈존- 아이들과 함께하는 행복한 식사
+현황 및 문제점
+- 노키즈존은 증가하고 있으나 월컴 키즈존은 부재한 상황임.
+- 일반 식당의 경우 어린이 메뉴가 없어 아이 식사에 어려움이 있고,
+- 어린이의 경우 식사가 일직 끝나 식당내에서 뛰어다는 상황으로 타인에게 방해를
+주는 불가피한 상황이 발생함.
+- 식당 공간내 놀이방 유무, 어린이 전용 메뉴 정보르 알고자 하나 안내 정보가
+정보가 없어 아이 양육에 힘든 상황이 가중되고 있음
+개선방안
+- 친절한 도시의 특징을 살리고자 독창적인 사업이 필요함
+“월컴키즈존” 알림문 부착, 식당 내 놀이방 설치 유무와 어린이 메뉴에 대한 정보를
+제공할 필요성이 있음.
+- “월컴 키즈존” 알림문에 놀이방 설치 유무, 어린이 메뉴, 관련정보를 볼 수 있는
+QR코드 표기를 통한 정보 제공
+- 시청 홈페에지에 메인 정보를 게시하고 시정 톡톡 링크와 알림문 내 QR코드를
+통한 해당 식당의 정보 제공
+기타
+- 공무원의 전수 조사 없이. 관련 협회의 협조 및
+식당의 자발적 신청에 따른 업무 진행으로 담당자 업부 피로도 최소화.
+기대효과
+- 월컴키즈존 (놀이방, 어린이메뉴) 정보 제공에 따른 유아 가구에 대한 식당 이용 정보 제공 등</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -11125,10 +13454,8 @@
           <t>2018-04-25</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+      <c r="E128" t="n">
+        <v>2018</v>
       </c>
       <c r="F128" t="n">
         <v>1</v>
@@ -11187,6 +13514,25 @@
         </is>
       </c>
       <c r="R128" t="inlineStr"/>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>2018. 4. 25.
+11:31 다산콜센터로 군자초등학교정문에서 동재아파트앞까지가 어린이보호구역인데 불법주차한차량이 많으니 단속요청을 했고 센터에서 단속하겠다고 하고 조금있다가 민원접수 되었다고 문자가 왔읍니다.
+13:54 현장확인후 이동조치 및 계도 조치하였다고 문자가 왔읍니다.
+밖을 내다보니 11:31분 제가 다산콜센터에 불법주차단속요청한 상태 그대로 였읍니다.
+13:57분경 문자를 보낸 02-2127-4900에 전화를 거니 동대문구청이었고 여직원이 받았읍니다.
+단속을 했다고 했는데 그대로다 어떻게 된거냐 했더니, 그렇게 구간으로 단속을 요청한것은 단속을 안하고 차 한대당 위치,차량번호,불법주차된주소, 불법주차시간등 적어서 을 한건씩 민원요청을 해야 단속한다고 했읍니다.....아니 불법주차한 곳이 도로인데 하나의 주차주소가 어디있나, 그냥 무슨건물 앞에 있는곳 하면 되는것 아니냐..어떻게 하나하나의 주차주소가 있을수 있나?.나는 지금까지 동재 아파트앞이 어린이 보호구역인데 와서 단속해달라고 해서 단속한줄 알았더니 그럼 하나도 단속한게 아니고 했다고 문자만 보낸것이냐,,그럼 애초에 그렇다고 애기를 해야지,단속한것처럼 속인것아닌가? 공무원 일하는 방식이 잘못된것이 아인가? 그많은 불법주차 차량을 일일이 하나 차량번호, 불법주차한 시간, 위치주소 어떻게 민원인이 일일이 신고해야 되는가? 등으로 언성이 있었지만,,,알았다고 전화 끝고 생활불편앱으로
+불법주차한 차량 한대씩 찍고 10분있다찍고 기다렸다가 불법주차 2~3대 사진찍어서 올리고 가 한시간이 다흘러 가서 짜증이 와서 그만 중간에 그만두고 말았읍니다.
+서울시민이 어린이보호구역에 불법주차한차량을 어떻게 하나하나 불법주차 시간까지 공증하면서 민원을 올려야 합니까?
+군자초등학교정문에서 동재아파트까지 불법주차 단속을 요청하면 하면 와서 단속을 하면 되지 않읍니까?
+서울시의 규정이 그렇다면  시민을 위한것으로 바꾸어 주시기 바라겠읍니다.</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -11209,10 +13555,8 @@
           <t>2018-04-19</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+      <c r="E129" t="n">
+        <v>2018</v>
       </c>
       <c r="F129" t="n">
         <v>11</v>
@@ -11271,6 +13615,17 @@
         </is>
       </c>
       <c r="R129" t="inlineStr"/>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>어린이 보호구역 내 횡단보도에 시인성이 확보된 안전휀스를 설치하여 교통사고로부터 어린이들을 보호하도록 개선합니다.
+자세한 것은 첨부파일을 참조바랍니다.</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -11293,10 +13648,8 @@
           <t>2018-04-17</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+      <c r="E130" t="n">
+        <v>2018</v>
       </c>
       <c r="F130" t="n">
         <v>0</v>
@@ -11355,6 +13708,29 @@
         </is>
       </c>
       <c r="R130" t="inlineStr"/>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>※ 운전자도 서울 시민입니다. ※
+운전자도 사람이고 행복/권리/건강을 누릴줄 알아야합니다.
+1). 어린이보호구역/스쿨존 대부분 속도제한 30km / 40km / 50km 대부분 입니다.
+밤 21:00(pm) ~ 6:00 까지는 제한속도를 풀어야한다고 봅니다. 자동차도 정상적으로 속도내야한다고 봅니다.
+제한속도 30km / 40km / 50km 떄문에 운전자도 조금이라도 일찍 집에들어가야 휴식을 취할 수 있기때문입니다.
+30분/1시간이라도 일찍 집에들어가서 휴식을 취할 수 있거나 숙면을 취해야 내일을 위한 활력소가 되기떄문입니다.
+(운전자도 일찍 집에들어가서 좋고 가족과 함꼐할 수 있는시간도 보내서 좋고)
+어린이는 21:00~22:00 꿈나라/대부분 잠자리에 들기떄문에 밤 늦으시간에는 돌아다니기보다는 집에 대부분 있습니다.
+유럽이나 선진국대부분은 보행자가 건너지않은곳은 자동으로 점멸등 으로 바뀌고 보행자가 건너가고싶을떄는 버튼눌러서 대부분 건너가고 있습니다. (보행자는 횡단보도 건너갈경우 버튼눌러서 30초후 건나갈 수 있게합니다.)
+) 시골/읍 지역은 20:00~21:00모든 신호 점멸등바귀고 서울시내 번화가/이동인구많은곳/차량이동많은곳 포함해서 23:00 ~ 5:00 보행자신호는 건너지않은곳도 상당히 많습니다.
+(2)  특히 출, 퇴근시간떄는 좌회전 신호가 상당히 많이 짧습니다.
+(좌회전 신호가 짧은 서울시내 엄청많습니다. 특히 출,퇴근 많이 막히는곳은 신호를 좀더 길게/여유있게 줘야한다고봅니다.)
+(3). 보행자가 건너지않기떄문에 차량운전자는 빨강신호등 멈춰야하는 불필요신호대기할 필요가 없다고봅니다.
+(4). 주말에는 전 구간 고속도로 통행료 무료했으면 합니다. (서울 남산톨게이트처럼요)</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -11377,10 +13753,8 @@
           <t>2018-04-10</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+      <c r="E131" t="n">
+        <v>2018</v>
       </c>
       <c r="F131" t="n">
         <v>0</v>
@@ -11439,6 +13813,62 @@
         </is>
       </c>
       <c r="R131" t="inlineStr"/>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>1995
+년도 어린이보호구역
+(
+스쿨존
+)
+제도가 도입되어
+유치원
+,
+초등학교
+,
+특수학교
+,
+어린이집
+,
+학원등의
+정문을 중심으로
+반경
+500
+미터이내의 일정구간을 스쿨존으로 지정관리하기위해
+스툴존의 도로를 다른색으로 표시해 좋았다
+.
+2011
+년 도로교통법 시행령이 개정되면서
+스쿨존내 속도위반
+,
+신호지시위반
+,
+횡단보도 보행자 횡단방해 보호불이행
+,
+주정차금지 위반시에는
+범칙금과 벌금을 일반도로에 비해 최대
+2
+배까지 부과한다
+.
+요즘 학교주변을 살펴보면
+,
+운전자들이 알기 쉽게 스쿨존의 도로를 다른색으로 표시해 놓았으나
+운전자들은 이를 무시하고 이행하지 않고 불법으로 주차하는 사례가 많다
+.
+도로교통법에 따라 교통사고의 위험을 사전 예방하기위해
+어린이보호구역
+(
+스쿨존
+)
+의 각종시설물에 대한 재정비와
+도로교통위반자에 대한 집중단속이 필요하다고 본다
+.</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -11461,10 +13891,8 @@
           <t>2018-04-07</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+      <c r="E132" t="n">
+        <v>2018</v>
       </c>
       <c r="F132" t="n">
         <v>12</v>
@@ -11523,6 +13951,20 @@
         </is>
       </c>
       <c r="R132" t="inlineStr"/>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>공공화장실
+,
+수유실 등에 기저귀교환대가 구비된 곳에는 살균소독기도      함께 비치하여 깨끗이 청소하고 사용할 수 있도록 개선합니다
+.
+첨부파일 참조바랍니다.</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -11545,10 +13987,8 @@
           <t>2018-03-30</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+      <c r="E133" t="n">
+        <v>2018</v>
       </c>
       <c r="F133" t="n">
         <v>0</v>
@@ -11607,6 +14047,29 @@
         </is>
       </c>
       <c r="R133" t="inlineStr"/>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>현재 어린이 보호구역(스쿨존)은 초등학교, 특수학교, 어린이집 등의 주변도로로 한정되어 있습니다. 이에 따라 중ㆍ고등학교 및 청소년 수련시설, 지역아동센터 등의 주변은 학생들의 유동이 많음에도 불구하고 안전이 보장되지 못하고 있습니다.
+보도블럭 위 불법주차 차량으로 인해 많은 청소년들은 인도가 아닌 차도로 통행을 해야 하거나, 횡단보도 옆에 주차된 차량으로 인해 시야가 가려져 운전자와 청소년들이 서로를 인지하지 못해 위험한 상황이 발생되기도 합니다.
+또한, 어린이 보호구역과 같은 별도의 속도제한 표지판이 없어 노란불에서도 속도를 올려 달리는 차량들도 쉽게 발견됩니다.
+따라서, 어린이 보호구역의 지정이 중ㆍ고등학교 및 청소년 수련시설 등으로 확대하여 아동 뿐만 아니라 청소년들의 안전도 보장해야 한다고 생각합니다.
+물론 도로교통법 상으로 규정된 사항이기에 제안의 실행이 쉽진 않을 수 있다고 생각이 되지만, 지자치단체에서도 차량 속도 제한 등의 정책은 별도로 진행하는 것으로 알고 있습니다. 지자체 소속 경찰청(서)와 협의하여 속도 제한이나 불법 주정차 단속부터 차례로 시행한다면 우리 청소년들의 안전도 보장할 수 있지 않을까 생각합니다.
+&lt;도로교통법&gt;
+제12조(어린이 보호구역의 지정 및 관리)  ①
+시장등은 교통사고의 위험으로부터 어린이를 보호하기 위하여 필요하다고 인정하는 경우에는 다음 각 호의 어느 하나에 해당하는 시설의 주변도로 가운데 일정 구간을 어린이 보호구역으로 지정하여 자동차등의 통행속도를 시속 30킬로미터 이내로 제한할 수 있다.
+1. 「유아교육법」 제2조에 따른 유치원, 「초ㆍ중등교육법」 제38조 및 제55조에 따른 초등학교 또는 특수학교
+2. 「영유아보육법」 제10조에 따른 어린이집 가운데 행정안전부령으로 정하는 어린이집
+3. 「학원의 설립ㆍ운영 및 과외교습에 관한 법률」 제2조에 따른 학원 가운데 행정안전부령으로 정하는 학원
+4. 「초ㆍ중등교육법」 제60조의2 또는 제60조의3에 따른 외국인학교 또는 대안학교, 「제주특별자치도 설치 및 국제자유도시 조성을 위한 특별법」 제223조에 따른 국제학교 및 「경제자유구역 및 제주국제자유도시의 외국교육기관 설립ㆍ운영에 관한 특별법」 제2조제2호에 따른 외국교육기관 중 유치원ㆍ초등학교 교과과정이 있는 학교
+② 제1항에 따른 어린이 보호구역의 지정절차 및 기준 등에 관하여 필요한 사항은 교육부, 행정안전부 및 국토교통부의 공동부령으로 정한다.
+③ 차마의 운전자는 어린이 보호구역에서 제1항에 따른 조치를 준수하고 어린이의 안전에 유의하면서 운행하여야 한다.</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -11629,10 +14092,8 @@
           <t>2018-03-13</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+      <c r="E134" t="n">
+        <v>2018</v>
       </c>
       <c r="F134" t="n">
         <v>9</v>
@@ -11691,6 +14152,20 @@
         </is>
       </c>
       <c r="R134" t="inlineStr"/>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>공공화장실
+,
+수유실 등에 기저귀교환대가 구비된 곳에는 살균소독기도      함께 비치하여 깨끗이 청소하고 사용할 수 있도록 개선합니다
+.
+첨부파일 참조바랍니다.</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -11713,10 +14188,8 @@
           <t>2018-03-13</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+      <c r="E135" t="n">
+        <v>2018</v>
       </c>
       <c r="F135" t="n">
         <v>8</v>
@@ -11775,6 +14248,17 @@
         </is>
       </c>
       <c r="R135" t="inlineStr"/>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>어린이 보호구역 내 횡단보도에 시인성이 확보된 안전휀스를 설치하여 교통사고로부터 어린이들을 보호하도록 개선
+첨부파일을 참조해주세요.</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -11797,10 +14281,8 @@
           <t>2018-02-26</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+      <c r="E136" t="n">
+        <v>2018</v>
       </c>
       <c r="F136" t="n">
         <v>0</v>
@@ -11859,6 +14341,67 @@
         </is>
       </c>
       <c r="R136" t="inlineStr"/>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>1995
+년도 어린이보호구역
+(
+스쿨존
+)
+제도가 도입되어
+유치원
+,
+초중등학교
+,
+특수학교
+,
+어린이집
+,
+학원등의
+정문을 중심으로
+반경
+500
+미터이내의 일정구간을 스쿨존으로 지정관리하기위해
+스툴존의 도로를 다른색으로 표시했다
+.
+2011
+년 도로교통법 시행령이 개정되면서
+스쿨존내 속도위반
+,
+신호지시위반
+,
+횡단보도 보행자 횡단방해 보호불이행
+,
+주정차금지 위반시에는
+범칙금과 벌금을 일반도로에 비해 최대
+2
+배까지 부과한다
+.
+요즘 학교주변을 살펴보면
+,
+운전자들이 알기 쉽게 스쿨존의 도로를 다른색으로 표시해 놓았으나
+운전자들은 이를 무시하고 이행하지 않고 불법으로 주차하는 사례가 많다
+.
+도로교통법에 따라 교통사고의 위험을 사전 예방하기위해
+어린이보호구역
+(
+스쿨존
+)
+의 각종시설물에 대한 재정비와
+도로교통위반자에 대한 집중단속이 필요하다고 본다
+.
+그리고
+,
+어린이 등하교시 교통사고예방을 위한
+스쿨존에 대한 안전준수사항 등의 홍보캠페인 등이 필요할 것 같다
+.</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -11881,10 +14424,8 @@
           <t>2018-02-21</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+      <c r="E137" t="n">
+        <v>2018</v>
       </c>
       <c r="F137" t="n">
         <v>10</v>
@@ -11943,6 +14484,40 @@
         </is>
       </c>
       <c r="R137" t="inlineStr"/>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>안녕하세요.
+서울 송파구 임산부 커뮤니티 송송마미입니다.
+우리 송송마미는 2015년 부터 엄마들의 친목으로 시작하여 지역사회 모자건강 증진을 위해 활동을 이어오고 있습니다.
+건의사항을 쓰기 이전에 우선 시민들이 안전하고 편리하게 지낼 수 있도록 노력해주심에 저희모두 항상 감사 말씀드립니다.
+본론으로 들어가서 육아 맘들의 입장에서 조금 더 개선되었으면 하는 부분이 있어 청원말씀드립니다.
+지하철 역사 내 수유실 개선문제입니다.
+지난 해 송송마미 운영진들이 발로뛰어 송파구 내 수유실 실태를 조사하고 부족한 부분을 채워주십사 청원 드렸었습니다. 그 후 많이 개선되었음을 기대하며 다시금 수유실 실태를 조사하였으나, 별로 달라진 부분이 없기도 하고 심지어 청결이나 편의시설에서 더 열악해 짐을 보고 실망하여 재차 청원말씀 드립니다.
+현황 및 문제점으로는 다음과 같습니다.
+첫째. 수유실을 이용하려 하면 직원에게 열쇠를 받아야하거나 직원이 없으면 수유실을 이용할 수 없습니다.
+둘째. 여름에는 습하고 덥고, 겨울에는 너무 추워서 수유하기에 어려운 환경입니다. 어른들이 이용하는 휴게공간이라면 온도는 그닥 중요치 않을수도 있습니다. 하지만 면역력이 약한 아기들은 1도에도 매우 민감하게 반응합니다.
+셋째. 하수구와 쓰레기통에서 냄새가 역류하고, 기저귀갈이대가 청결하지 않아 사용하기에 불쾌한 환경입니다.
+넷째. 엄마들이 챙겨야 하지만 급하다보면 물티슈 등을 빠뜨릴때가 있는데 수유실에 비치되지 않아 곤란한 환경입니다.
+개선방안으로는 다음과 같습니다.
+첫째. 상시 개방이 필요합니다. 지하철이 운영되지 않는 시간은 닫혀 있더라도 운영시간 내에는 언제든 이용할 수 있도록 열려있으면 좋겠습니다.
+둘째. 적절한 온도가 필요합니다. 동절기는 최소 22도 이상의 따뜻한 온도, 하절기는 최대26도 이하의 시원한 온도이면 좋겠습니다.
+셋째. 위생적인 실내환경이 필요합니다. 구체적으로는 냄새가 역류하지않는 하수구와 쓰레기통이 구비되어 있었으면 좋겠고 기저귀갈이대도 잘 닦여있었으면 좋겠습니다. 주기적으로 환기를 해 주어 실내공기의 쾌적함도 유지해 주세요.
+넷째. 각종 물품이 구비되어 있어야 합니다. 기본적인 물티슈, 티슈, 전자렌지, 수유쿠션, 일반쿠션, 1개정도의 아기의자 등이 필요합니다.
+출산율이 계속 감소하여 정부에서는 출산장려 정책을 내놓고 있지만 임산부 요구도 반영보다는 다른 방향으로정책을 내고 있습니다.
+수유하기 편하고 수유하기 좋은 환경이어야 모유수유율도 높아지고 육아 환경이 개선 되어야(그 밖에 개선되어야 하는 부분이 많지만) 출산율도 높아진다고 생각합니다.
+수유하기편하고 쾌적한 환경을 조성함으로써, 지하철 이용 엄마와아가의 지하철 이용 만족도가 높아집니다.
+아이와 함께 외출한 엄마는 더이상 더 쾌적한 환경의 수유실을 찾아 헤매지 않아도 되며, 지하철이 편리함을 느낀 엄마들은 자가용으로 이동하는 대신 지하철로 이동하는 선택을 할 수 있습니다. 크게 보면 대중교통이용증가로 인한 교통제증저하, 미세먼지 저하, 매연감소로 인한 대기오염저하 등 기대효과가 매우 광범위하게 크지만, 저희가 추구하는 기대효과는 &lt;육아맘들의 편리한 수유실이용&gt;입니다.
+이는 곧 육아환경의 개선으로 이어져 출산률증대까지 이어질 수 있습니다.
+여전히 역 내 수유실이 쾌적하지 않다는 이유로 더 나은 환경의 수유실을 찾아다니는 엄마들이 많습니다.
+엄마들이 더욱 쾌적하고 위생적인 환경에서 수유 할 수 있도록 역 내 수유실 환경 개선에 힘써주심을 정중히 부탁드립니다.
+한번에 바꾸기가 결코 쉽지 않다는 것. 알고 있습니다. 작은 퍼즐하나하나 채워나가다보면 어느새 큰 그림이 맞춰져 있으리라 믿고 작은 변화하나라도 기다리겠습니다. 감사합니다.</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -11965,10 +14540,8 @@
           <t>2018-02-17</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+      <c r="E138" t="n">
+        <v>2018</v>
       </c>
       <c r="F138" t="n">
         <v>2</v>
@@ -12027,6 +14600,20 @@
         </is>
       </c>
       <c r="R138" t="inlineStr"/>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>● 현황 및 문제점
+아기들에게 예방접종은 감염병을 예방하기 위한 가장 효과적인 방법으로 「감염병의 예방 및 관리에 관한 법률」제24조 및 제25조에 따른 정기 및 임시예방접종에 대한 예방접종을 실시한 경우 법 제28조에 따라 예방접종의 기록를 작성하고 보고(전자문서 포함)하도록 하고 있습니다. 또한 질병관리본부는 2002년부터 개인별 예방접종기록을 전산화하는 ‘예방접종등록사업’을 추진하고 있지만 현재까지 예방접종기록의 전산등록이 의무사항은 아닌 사항으로 전산등록을 위한 홍보도 필요하지만 무엇보다 서울시 25개 자치구청 보건소에서 예방접종을 할 경우에는 가능한 전원 전산등록을 하도록 업무 개선토록 하는 것입니다.
+사실 전산등록을 안할 경우에 종이로 보존하는 문서는 즉 예방접종 의료기록이 일정기간이 지나면 자동폐기 되므로 성인이 되어서 예방접종진료을 확인하려고 해도 기록이 없어서 확인할 수 있는 방법이 없어서 많은 어려움 겪는 실정으로 개선이 필요한 실정입니다
+● 개선방안
+서울시에서는 서울시 25개 자치구청 보건소 예방 접종 기록 담당자들과 업무 협의를 통하여 서울시민(아기)들이 서울시 25개 자치구청 보건소에서 예방 접종을 할 경우 특별한 경우를 제외하고 가능한 모두 예방 접종에 대하여 전산에 등록토록 업무를 개선하여 예방 접종 기록을 장기 보존토록 예방접종 업무를 개선토록 하는 것입니다.</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>웹크롤링 성공</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
